--- a/research/traditional_assets/database/data/tunisia/tunisia_building_materials.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_building_materials.xlsx
@@ -1650,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1787,22 +1787,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1963287823985727</v>
+        <v>0.1960725392249749</v>
       </c>
       <c r="C2">
-        <v>131.9774696301417</v>
+        <v>130.9612934326492</v>
       </c>
       <c r="D2">
-        <v>130.0874696301417</v>
+        <v>130.3092934326492</v>
       </c>
       <c r="E2">
-        <v>-24.3</v>
+        <v>-23.062</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.238</v>
       </c>
       <c r="G2">
         <v>1.89</v>
@@ -1823,28 +1823,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0622714</v>
       </c>
       <c r="N2">
-        <v>15.6234693877551</v>
+        <v>15.5611979877551</v>
       </c>
       <c r="O2">
-        <v>2.343520408163265</v>
+        <v>2.334179698163265</v>
       </c>
       <c r="P2">
-        <v>13.27994897959184</v>
+        <v>13.22701828959184</v>
       </c>
       <c r="Q2">
-        <v>16.32994897959184</v>
+        <v>16.27701828959184</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1963287823985727</v>
+        <v>0.1976212012373484</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9285195673476866</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>250.8931770886009</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1869,22 +1869,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1960725392249749</v>
+        <v>0.195816296051377</v>
       </c>
       <c r="C3">
-        <v>130.9612934326492</v>
+        <v>129.9458750306313</v>
       </c>
       <c r="D3">
-        <v>130.3092934326492</v>
+        <v>130.5318750306313</v>
       </c>
       <c r="E3">
-        <v>-23.062</v>
+        <v>-21.824</v>
       </c>
       <c r="F3">
-        <v>1.238</v>
+        <v>2.476</v>
       </c>
       <c r="G3">
         <v>1.89</v>
@@ -1905,28 +1905,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M3">
-        <v>0.0622714</v>
+        <v>0.1245428</v>
       </c>
       <c r="N3">
-        <v>15.5611979877551</v>
+        <v>15.4989265877551</v>
       </c>
       <c r="O3">
-        <v>2.334179698163265</v>
+        <v>2.324838988163265</v>
       </c>
       <c r="P3">
-        <v>13.22701828959184</v>
+        <v>13.17408759959184</v>
       </c>
       <c r="Q3">
-        <v>16.27701828959184</v>
+        <v>16.22408759959184</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1976212012373484</v>
+        <v>0.1989399959707929</v>
       </c>
       <c r="T3">
-        <v>0.9285195673476866</v>
+        <v>0.9365851517676385</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>250.8931770886009</v>
+        <v>125.4465885443004</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.195816296051377</v>
+        <v>0.1955600528777791</v>
       </c>
       <c r="C4">
-        <v>129.9458750306313</v>
+        <v>128.9312183139088</v>
       </c>
       <c r="D4">
-        <v>130.5318750306313</v>
+        <v>130.7552183139088</v>
       </c>
       <c r="E4">
-        <v>-21.824</v>
+        <v>-20.586</v>
       </c>
       <c r="F4">
-        <v>2.476</v>
+        <v>3.714</v>
       </c>
       <c r="G4">
         <v>1.89</v>
@@ -1987,28 +1987,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M4">
-        <v>0.1245428</v>
+        <v>0.1868142</v>
       </c>
       <c r="N4">
-        <v>15.4989265877551</v>
+        <v>15.4366551877551</v>
       </c>
       <c r="O4">
-        <v>2.324838988163265</v>
+        <v>2.315498278163265</v>
       </c>
       <c r="P4">
-        <v>13.17408759959184</v>
+        <v>13.12115690959184</v>
       </c>
       <c r="Q4">
-        <v>16.22408759959184</v>
+        <v>16.17115690959184</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1989399959707929</v>
+        <v>0.2002859823482259</v>
       </c>
       <c r="T4">
-        <v>0.9365851517676385</v>
+        <v>0.9448170368972797</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>125.4465885443004</v>
+        <v>83.63105902953363</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2033,22 +2033,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1955600528777791</v>
+        <v>0.1953038097041813</v>
       </c>
       <c r="C5">
-        <v>128.9312183139088</v>
+        <v>127.9173271989702</v>
       </c>
       <c r="D5">
-        <v>130.7552183139088</v>
+        <v>130.9793271989702</v>
       </c>
       <c r="E5">
-        <v>-20.586</v>
+        <v>-19.348</v>
       </c>
       <c r="F5">
-        <v>3.714</v>
+        <v>4.952</v>
       </c>
       <c r="G5">
         <v>1.89</v>
@@ -2069,28 +2069,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M5">
-        <v>0.1868142</v>
+        <v>0.2490856</v>
       </c>
       <c r="N5">
-        <v>15.4366551877551</v>
+        <v>15.3743837877551</v>
       </c>
       <c r="O5">
-        <v>2.315498278163265</v>
+        <v>2.306157568163265</v>
       </c>
       <c r="P5">
-        <v>13.12115690959184</v>
+        <v>13.06822621959184</v>
       </c>
       <c r="Q5">
-        <v>16.17115690959184</v>
+        <v>16.11822621959184</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2002859823482259</v>
+        <v>0.2016600101085222</v>
       </c>
       <c r="T5">
-        <v>0.9448170368972797</v>
+        <v>0.9532204196337888</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>83.63105902953363</v>
+        <v>62.72329427215022</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2115,22 +2115,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1953038097041813</v>
+        <v>0.1950475665305834</v>
       </c>
       <c r="C6">
-        <v>127.9173271989702</v>
+        <v>126.9042056292011</v>
       </c>
       <c r="D6">
-        <v>130.9793271989702</v>
+        <v>131.2042056292011</v>
       </c>
       <c r="E6">
-        <v>-19.348</v>
+        <v>-18.11</v>
       </c>
       <c r="F6">
-        <v>4.952</v>
+        <v>6.19</v>
       </c>
       <c r="G6">
         <v>1.89</v>
@@ -2151,28 +2151,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M6">
-        <v>0.2490856</v>
+        <v>0.311357</v>
       </c>
       <c r="N6">
-        <v>15.3743837877551</v>
+        <v>15.3121123877551</v>
       </c>
       <c r="O6">
-        <v>2.306157568163265</v>
+        <v>2.296816858163265</v>
       </c>
       <c r="P6">
-        <v>13.06822621959184</v>
+        <v>13.01529552959184</v>
       </c>
       <c r="Q6">
-        <v>16.11822621959184</v>
+        <v>16.06529552959184</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2016600101085222</v>
+        <v>0.2030629647690352</v>
       </c>
       <c r="T6">
-        <v>0.9532204196337888</v>
+        <v>0.9618007156910663</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>62.72329427215022</v>
+        <v>50.17863541772018</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2197,22 +2197,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1950475665305834</v>
+        <v>0.1947913233569856</v>
       </c>
       <c r="C7">
-        <v>126.9042056292011</v>
+        <v>125.8918575751152</v>
       </c>
       <c r="D7">
-        <v>131.2042056292011</v>
+        <v>131.4298575751152</v>
       </c>
       <c r="E7">
-        <v>-18.11</v>
+        <v>-16.872</v>
       </c>
       <c r="F7">
-        <v>6.19</v>
+        <v>7.428000000000001</v>
       </c>
       <c r="G7">
         <v>1.89</v>
@@ -2233,28 +2233,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M7">
-        <v>0.311357</v>
+        <v>0.3736284</v>
       </c>
       <c r="N7">
-        <v>15.3121123877551</v>
+        <v>15.2498409877551</v>
       </c>
       <c r="O7">
-        <v>2.296816858163265</v>
+        <v>2.287476148163265</v>
       </c>
       <c r="P7">
-        <v>13.01529552959184</v>
+        <v>12.96236483959184</v>
       </c>
       <c r="Q7">
-        <v>16.06529552959184</v>
+        <v>16.01236483959184</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2030629647690352</v>
+        <v>0.2044957695287081</v>
       </c>
       <c r="T7">
-        <v>0.9618007156910663</v>
+        <v>0.9705635712389242</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>50.17863541772018</v>
+        <v>41.81552951476682</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2279,22 +2279,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1947913233569856</v>
+        <v>0.1945350801833877</v>
       </c>
       <c r="C8">
-        <v>125.8918575751152</v>
+        <v>124.8802870345879</v>
       </c>
       <c r="D8">
-        <v>131.4298575751152</v>
+        <v>131.6562870345879</v>
       </c>
       <c r="E8">
-        <v>-16.872</v>
+        <v>-15.634</v>
       </c>
       <c r="F8">
-        <v>7.428</v>
+        <v>8.665999999999999</v>
       </c>
       <c r="G8">
         <v>1.89</v>
@@ -2315,28 +2315,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M8">
-        <v>0.3736284</v>
+        <v>0.4358997999999999</v>
       </c>
       <c r="N8">
-        <v>15.2498409877551</v>
+        <v>15.1875695877551</v>
       </c>
       <c r="O8">
-        <v>2.287476148163265</v>
+        <v>2.278135438163265</v>
       </c>
       <c r="P8">
-        <v>12.96236483959184</v>
+        <v>12.90943414959184</v>
       </c>
       <c r="Q8">
-        <v>16.01236483959184</v>
+        <v>15.95943414959184</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2044957695287081</v>
+        <v>0.2059593872939653</v>
       </c>
       <c r="T8">
-        <v>0.9705635712389242</v>
+        <v>0.9795148752931877</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>41.81552951476682</v>
+        <v>35.84188244122871</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2361,22 +2361,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1945350801833877</v>
+        <v>0.1942788370097899</v>
       </c>
       <c r="C9">
-        <v>124.8802870345879</v>
+        <v>123.8694980330929</v>
       </c>
       <c r="D9">
-        <v>131.6562870345879</v>
+        <v>131.8834980330929</v>
       </c>
       <c r="E9">
-        <v>-15.634</v>
+        <v>-14.396</v>
       </c>
       <c r="F9">
-        <v>8.666</v>
+        <v>9.904</v>
       </c>
       <c r="G9">
         <v>1.89</v>
@@ -2397,28 +2397,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M9">
-        <v>0.4358998</v>
+        <v>0.4981712</v>
       </c>
       <c r="N9">
-        <v>15.1875695877551</v>
+        <v>15.1252981877551</v>
       </c>
       <c r="O9">
-        <v>2.278135438163265</v>
+        <v>2.268794728163265</v>
       </c>
       <c r="P9">
-        <v>12.90943414959184</v>
+        <v>12.85650345959184</v>
       </c>
       <c r="Q9">
-        <v>15.95943414959184</v>
+        <v>15.90650345959184</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2059593872939653</v>
+        <v>0.2074548228367281</v>
       </c>
       <c r="T9">
-        <v>0.9795148752931877</v>
+        <v>0.9886607729138482</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>35.8418824412287</v>
+        <v>31.36164713607511</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2443,22 +2443,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1942788370097899</v>
+        <v>0.194022593836192</v>
       </c>
       <c r="C10">
-        <v>123.8694980330929</v>
+        <v>122.8594946239401</v>
       </c>
       <c r="D10">
-        <v>131.8834980330929</v>
+        <v>132.1114946239401</v>
       </c>
       <c r="E10">
-        <v>-14.396</v>
+        <v>-13.158</v>
       </c>
       <c r="F10">
-        <v>9.904</v>
+        <v>11.142</v>
       </c>
       <c r="G10">
         <v>1.89</v>
@@ -2479,28 +2479,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M10">
-        <v>0.4981712</v>
+        <v>0.5604425999999999</v>
       </c>
       <c r="N10">
-        <v>15.1252981877551</v>
+        <v>15.0630267877551</v>
       </c>
       <c r="O10">
-        <v>2.268794728163265</v>
+        <v>2.259454018163265</v>
       </c>
       <c r="P10">
-        <v>12.85650345959184</v>
+        <v>12.80357276959184</v>
       </c>
       <c r="Q10">
-        <v>15.90650345959184</v>
+        <v>15.85357276959184</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2074548228367281</v>
+        <v>0.2089831250947165</v>
       </c>
       <c r="T10">
-        <v>0.9886607729138482</v>
+        <v>0.9980076792734244</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.36164713607511</v>
+        <v>27.87701967651121</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2525,22 +2525,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.194022593836192</v>
+        <v>0.1937663506625942</v>
       </c>
       <c r="C11">
-        <v>122.8594946239401</v>
+        <v>121.8502808885172</v>
       </c>
       <c r="D11">
-        <v>132.1114946239401</v>
+        <v>132.3402808885172</v>
       </c>
       <c r="E11">
-        <v>-13.158</v>
+        <v>-11.92</v>
       </c>
       <c r="F11">
-        <v>11.142</v>
+        <v>12.38</v>
       </c>
       <c r="G11">
         <v>1.89</v>
@@ -2561,28 +2561,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M11">
-        <v>0.5604425999999999</v>
+        <v>0.6227139999999999</v>
       </c>
       <c r="N11">
-        <v>15.0630267877551</v>
+        <v>15.0007553877551</v>
       </c>
       <c r="O11">
-        <v>2.259454018163265</v>
+        <v>2.250113308163265</v>
       </c>
       <c r="P11">
-        <v>12.80357276959184</v>
+        <v>12.75064207959184</v>
       </c>
       <c r="Q11">
-        <v>15.85357276959184</v>
+        <v>15.80064207959184</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2089831250947165</v>
+        <v>0.2105453896251046</v>
       </c>
       <c r="T11">
-        <v>0.9980076792734244</v>
+        <v>1.007562294663213</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>27.87701967651121</v>
+        <v>25.08931770886009</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2607,22 +2607,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1937663506625942</v>
+        <v>0.1935101074889963</v>
       </c>
       <c r="C12">
-        <v>121.8502808885172</v>
+        <v>120.8418609365327</v>
       </c>
       <c r="D12">
-        <v>132.3402808885172</v>
+        <v>132.5698609365327</v>
       </c>
       <c r="E12">
-        <v>-11.92</v>
+        <v>-10.682</v>
       </c>
       <c r="F12">
-        <v>12.38</v>
+        <v>13.618</v>
       </c>
       <c r="G12">
         <v>1.89</v>
@@ -2643,28 +2643,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M12">
-        <v>0.622714</v>
+        <v>0.6849854</v>
       </c>
       <c r="N12">
-        <v>15.0007553877551</v>
+        <v>14.9384839877551</v>
       </c>
       <c r="O12">
-        <v>2.250113308163265</v>
+        <v>2.240772598163265</v>
       </c>
       <c r="P12">
-        <v>12.75064207959184</v>
+        <v>12.69771138959184</v>
       </c>
       <c r="Q12">
-        <v>15.80064207959184</v>
+        <v>15.74771138959184</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2105453896251046</v>
+        <v>0.2121427612235914</v>
       </c>
       <c r="T12">
-        <v>1.007562294663213</v>
+        <v>1.0173316205112</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.08931770886009</v>
+        <v>22.80847064441826</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2689,22 +2689,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1935101074889963</v>
+        <v>0.1932538643153984</v>
       </c>
       <c r="C13">
-        <v>120.8418609365327</v>
+        <v>119.8342389062626</v>
       </c>
       <c r="D13">
-        <v>132.5698609365327</v>
+        <v>132.8002389062626</v>
       </c>
       <c r="E13">
-        <v>-10.682</v>
+        <v>-9.444000000000001</v>
       </c>
       <c r="F13">
-        <v>13.618</v>
+        <v>14.856</v>
       </c>
       <c r="G13">
         <v>1.89</v>
@@ -2725,28 +2725,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M13">
-        <v>0.6849854</v>
+        <v>0.7472567999999999</v>
       </c>
       <c r="N13">
-        <v>14.9384839877551</v>
+        <v>14.8762125877551</v>
       </c>
       <c r="O13">
-        <v>2.240772598163265</v>
+        <v>2.231431888163265</v>
       </c>
       <c r="P13">
-        <v>12.69771138959184</v>
+        <v>12.64478069959184</v>
       </c>
       <c r="Q13">
-        <v>15.74771138959184</v>
+        <v>15.69478069959183</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2121427612235914</v>
+        <v>0.2137764367220437</v>
       </c>
       <c r="T13">
-        <v>1.0173316205112</v>
+        <v>1.027322976492095</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.80847064441826</v>
+        <v>20.90776475738341</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2771,22 +2771,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1932538643153984</v>
+        <v>0.1929976211418006</v>
       </c>
       <c r="C14">
-        <v>119.8342389062626</v>
+        <v>118.8274189647984</v>
       </c>
       <c r="D14">
-        <v>132.8002389062626</v>
+        <v>133.0314189647984</v>
       </c>
       <c r="E14">
-        <v>-9.444000000000001</v>
+        <v>-8.206</v>
       </c>
       <c r="F14">
-        <v>14.856</v>
+        <v>16.094</v>
       </c>
       <c r="G14">
         <v>1.89</v>
@@ -2807,28 +2807,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M14">
-        <v>0.7472567999999999</v>
+        <v>0.8095282</v>
       </c>
       <c r="N14">
-        <v>14.8762125877551</v>
+        <v>14.8139411877551</v>
       </c>
       <c r="O14">
-        <v>2.231431888163265</v>
+        <v>2.222091178163265</v>
       </c>
       <c r="P14">
-        <v>12.64478069959184</v>
+        <v>12.59185000959184</v>
       </c>
       <c r="Q14">
-        <v>15.69478069959183</v>
+        <v>15.64185000959183</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2137764367220437</v>
+        <v>0.2154476679790811</v>
       </c>
       <c r="T14">
-        <v>1.027322976492095</v>
+        <v>1.037544018817379</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.90776475738341</v>
+        <v>19.2994751606616</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2853,22 +2853,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1929976211418006</v>
+        <v>0.1927413779682027</v>
       </c>
       <c r="C15">
-        <v>118.8274189647984</v>
+        <v>117.8214053082989</v>
       </c>
       <c r="D15">
-        <v>133.0314189647984</v>
+        <v>133.2634053082989</v>
       </c>
       <c r="E15">
-        <v>-8.206</v>
+        <v>-6.968</v>
       </c>
       <c r="F15">
-        <v>16.094</v>
+        <v>17.332</v>
       </c>
       <c r="G15">
         <v>1.89</v>
@@ -2889,28 +2889,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M15">
-        <v>0.8095282</v>
+        <v>0.8717996</v>
       </c>
       <c r="N15">
-        <v>14.8139411877551</v>
+        <v>14.7516697877551</v>
       </c>
       <c r="O15">
-        <v>2.222091178163265</v>
+        <v>2.212750468163265</v>
       </c>
       <c r="P15">
-        <v>12.59185000959184</v>
+        <v>12.53891931959184</v>
       </c>
       <c r="Q15">
-        <v>15.64185000959183</v>
+        <v>15.58891931959184</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2154476679790811</v>
+        <v>0.2171577650793055</v>
       </c>
       <c r="T15">
-        <v>1.037544018817379</v>
+        <v>1.04800275980139</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.2994751606616</v>
+        <v>17.92094122061435</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2935,22 +2935,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1927413779682027</v>
+        <v>0.1924851347946049</v>
       </c>
       <c r="C16">
-        <v>117.8214053082989</v>
+        <v>116.8162021622437</v>
       </c>
       <c r="D16">
-        <v>133.2634053082989</v>
+        <v>133.4962021622437</v>
       </c>
       <c r="E16">
-        <v>-6.968</v>
+        <v>-5.729999999999997</v>
       </c>
       <c r="F16">
-        <v>17.332</v>
+        <v>18.57</v>
       </c>
       <c r="G16">
         <v>1.89</v>
@@ -2971,28 +2971,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M16">
-        <v>0.8717996</v>
+        <v>0.9340710000000001</v>
       </c>
       <c r="N16">
-        <v>14.7516697877551</v>
+        <v>14.6893983877551</v>
       </c>
       <c r="O16">
-        <v>2.212750468163265</v>
+        <v>2.203409758163265</v>
       </c>
       <c r="P16">
-        <v>12.53891931959184</v>
+        <v>12.48598862959184</v>
       </c>
       <c r="Q16">
-        <v>15.58891931959184</v>
+        <v>15.53598862959184</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2171577650793055</v>
+        <v>0.2189080997583586</v>
       </c>
       <c r="T16">
-        <v>1.04800275980139</v>
+        <v>1.058707588808554</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.92094122061435</v>
+        <v>16.72621180590672</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1924851347946049</v>
+        <v>0.192228891621007</v>
       </c>
       <c r="C17">
-        <v>116.8162021622437</v>
+        <v>115.81181378169</v>
       </c>
       <c r="D17">
-        <v>133.4962021622437</v>
+        <v>133.72981378169</v>
       </c>
       <c r="E17">
-        <v>-5.73</v>
+        <v>-4.492000000000001</v>
       </c>
       <c r="F17">
-        <v>18.57</v>
+        <v>19.808</v>
       </c>
       <c r="G17">
         <v>1.89</v>
@@ -3053,28 +3053,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M17">
-        <v>0.934071</v>
+        <v>0.9963424</v>
       </c>
       <c r="N17">
-        <v>14.6893983877551</v>
+        <v>14.6271269877551</v>
       </c>
       <c r="O17">
-        <v>2.203409758163265</v>
+        <v>2.194069048163265</v>
       </c>
       <c r="P17">
-        <v>12.48598862959184</v>
+        <v>12.43305793959184</v>
       </c>
       <c r="Q17">
-        <v>15.53598862959184</v>
+        <v>15.48305793959184</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2189080997583586</v>
+        <v>0.2207001090726274</v>
       </c>
       <c r="T17">
-        <v>1.058707588808554</v>
+        <v>1.069667294696842</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.72621180590673</v>
+        <v>15.68082356803756</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3099,22 +3099,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.192228891621007</v>
+        <v>0.1919726484474091</v>
       </c>
       <c r="C18">
-        <v>115.81181378169</v>
+        <v>114.8082444515318</v>
       </c>
       <c r="D18">
-        <v>133.72981378169</v>
+        <v>133.9642444515318</v>
       </c>
       <c r="E18">
-        <v>-4.492000000000001</v>
+        <v>-3.254000000000001</v>
       </c>
       <c r="F18">
-        <v>19.808</v>
+        <v>21.046</v>
       </c>
       <c r="G18">
         <v>1.89</v>
@@ -3135,28 +3135,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M18">
-        <v>0.9963424</v>
+        <v>1.0586138</v>
       </c>
       <c r="N18">
-        <v>14.6271269877551</v>
+        <v>14.5648555877551</v>
       </c>
       <c r="O18">
-        <v>2.194069048163265</v>
+        <v>2.184728338163265</v>
       </c>
       <c r="P18">
-        <v>12.43305793959184</v>
+        <v>12.38012724959184</v>
       </c>
       <c r="Q18">
-        <v>15.48305793959184</v>
+        <v>15.43012724959184</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2207001090726274</v>
+        <v>0.2225352993342279</v>
       </c>
       <c r="T18">
-        <v>1.069667294696842</v>
+        <v>1.080891089883642</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.68082356803756</v>
+        <v>14.75842218168241</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3181,22 +3181,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1919726484474091</v>
+        <v>0.1917164052738113</v>
       </c>
       <c r="C19">
-        <v>114.8082444515318</v>
+        <v>113.8054984867617</v>
       </c>
       <c r="D19">
-        <v>133.9642444515318</v>
+        <v>134.1994984867617</v>
       </c>
       <c r="E19">
-        <v>-3.254000000000001</v>
+        <v>-2.015999999999998</v>
       </c>
       <c r="F19">
-        <v>21.046</v>
+        <v>22.284</v>
       </c>
       <c r="G19">
         <v>1.89</v>
@@ -3217,28 +3217,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M19">
-        <v>1.0586138</v>
+        <v>1.1208852</v>
       </c>
       <c r="N19">
-        <v>14.5648555877551</v>
+        <v>14.5025841877551</v>
       </c>
       <c r="O19">
-        <v>2.184728338163265</v>
+        <v>2.175387628163265</v>
       </c>
       <c r="P19">
-        <v>12.38012724959184</v>
+        <v>12.32719655959184</v>
       </c>
       <c r="Q19">
-        <v>15.43012724959184</v>
+        <v>15.37719655959184</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2225352993342279</v>
+        <v>0.2244152503339162</v>
       </c>
       <c r="T19">
-        <v>1.080891089883642</v>
+        <v>1.092388636172559</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.75842218168241</v>
+        <v>13.9385098382556</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3263,22 +3263,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1917164052738113</v>
+        <v>0.1914601621002134</v>
       </c>
       <c r="C20">
-        <v>113.8054984867616</v>
+        <v>112.8035802327358</v>
       </c>
       <c r="D20">
-        <v>134.1994984867617</v>
+        <v>134.4355802327358</v>
       </c>
       <c r="E20">
-        <v>-2.016000000000002</v>
+        <v>-0.7780000000000022</v>
       </c>
       <c r="F20">
-        <v>22.284</v>
+        <v>23.522</v>
       </c>
       <c r="G20">
         <v>1.89</v>
@@ -3299,28 +3299,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M20">
-        <v>1.1208852</v>
+        <v>1.1831566</v>
       </c>
       <c r="N20">
-        <v>14.5025841877551</v>
+        <v>14.4403127877551</v>
       </c>
       <c r="O20">
-        <v>2.175387628163265</v>
+        <v>2.166046918163265</v>
       </c>
       <c r="P20">
-        <v>12.32719655959184</v>
+        <v>12.27426586959184</v>
       </c>
       <c r="Q20">
-        <v>15.37719655959184</v>
+        <v>15.32426586959184</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2244152503339162</v>
+        <v>0.2263416198768067</v>
       </c>
       <c r="T20">
-        <v>1.092388636172559</v>
+        <v>1.104170072493301</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>13.93850983825561</v>
+        <v>13.20490405729478</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3345,22 +3345,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1914601621002134</v>
+        <v>0.1914589189266156</v>
       </c>
       <c r="C21">
-        <v>112.8035802327358</v>
+        <v>111.5667276170854</v>
       </c>
       <c r="D21">
-        <v>134.4355802327358</v>
+        <v>134.4367276170854</v>
       </c>
       <c r="E21">
-        <v>-0.7780000000000022</v>
+        <v>0.4600000000000009</v>
       </c>
       <c r="F21">
-        <v>23.522</v>
+        <v>24.76</v>
       </c>
       <c r="G21">
         <v>1.89</v>
@@ -3381,45 +3381,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M21">
-        <v>1.1831566</v>
+        <v>1.282568</v>
       </c>
       <c r="N21">
-        <v>14.4403127877551</v>
+        <v>14.3409013877551</v>
       </c>
       <c r="O21">
-        <v>2.166046918163265</v>
+        <v>2.151135208163265</v>
       </c>
       <c r="P21">
-        <v>12.27426586959184</v>
+        <v>12.18976617959184</v>
       </c>
       <c r="Q21">
-        <v>15.32426586959184</v>
+        <v>15.23976617959184</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2263416198768067</v>
+        <v>0.2283161486582694</v>
       </c>
       <c r="T21">
-        <v>1.104170072493301</v>
+        <v>1.116246044722062</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.20490405729478</v>
+        <v>12.18139653239056</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3427,22 +3427,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1914589189266156</v>
+        <v>0.1912154257530177</v>
       </c>
       <c r="C22">
-        <v>111.5667276170854</v>
+        <v>110.5538373348893</v>
       </c>
       <c r="D22">
-        <v>134.4367276170854</v>
+        <v>134.6618373348893</v>
       </c>
       <c r="E22">
-        <v>0.4600000000000009</v>
+        <v>1.698</v>
       </c>
       <c r="F22">
-        <v>24.76</v>
+        <v>25.998</v>
       </c>
       <c r="G22">
         <v>1.89</v>
@@ -3463,28 +3463,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M22">
-        <v>1.282568</v>
+        <v>1.3466964</v>
       </c>
       <c r="N22">
-        <v>14.3409013877551</v>
+        <v>14.2767729877551</v>
       </c>
       <c r="O22">
-        <v>2.151135208163265</v>
+        <v>2.141515948163265</v>
       </c>
       <c r="P22">
-        <v>12.18976617959184</v>
+        <v>12.13525703959183</v>
       </c>
       <c r="Q22">
-        <v>15.23976617959184</v>
+        <v>15.18525703959184</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2283161486582694</v>
+        <v>0.230340665510149</v>
       </c>
       <c r="T22">
-        <v>1.116246044722062</v>
+        <v>1.128627737766742</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.18139653239056</v>
+        <v>11.60133003084816</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3509,22 +3509,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1912154257530177</v>
+        <v>0.1909719325794199</v>
       </c>
       <c r="C23">
-        <v>110.5538373348893</v>
+        <v>109.5417021942501</v>
       </c>
       <c r="D23">
-        <v>134.6618373348893</v>
+        <v>134.8877021942501</v>
       </c>
       <c r="E23">
-        <v>1.697999999999997</v>
+        <v>2.936</v>
       </c>
       <c r="F23">
-        <v>25.998</v>
+        <v>27.236</v>
       </c>
       <c r="G23">
         <v>1.89</v>
@@ -3545,28 +3545,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M23">
-        <v>1.3466964</v>
+        <v>1.4108248</v>
       </c>
       <c r="N23">
-        <v>14.2767729877551</v>
+        <v>14.2126445877551</v>
       </c>
       <c r="O23">
-        <v>2.141515948163265</v>
+        <v>2.131896688163265</v>
       </c>
       <c r="P23">
-        <v>12.13525703959184</v>
+        <v>12.08074789959184</v>
       </c>
       <c r="Q23">
-        <v>15.18525703959184</v>
+        <v>15.13074789959184</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.230340665510149</v>
+        <v>0.2324170930505383</v>
       </c>
       <c r="T23">
-        <v>1.128627737766741</v>
+        <v>1.141326910120259</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.60133003084816</v>
+        <v>11.07399684762778</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3591,22 +3591,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1909719325794199</v>
+        <v>0.190728439405822</v>
       </c>
       <c r="C24">
-        <v>109.5417021942501</v>
+        <v>108.5303260012907</v>
       </c>
       <c r="D24">
-        <v>134.8877021942501</v>
+        <v>135.1143260012907</v>
       </c>
       <c r="E24">
-        <v>2.936</v>
+        <v>4.173999999999999</v>
       </c>
       <c r="F24">
-        <v>27.236</v>
+        <v>28.474</v>
       </c>
       <c r="G24">
         <v>1.89</v>
@@ -3627,28 +3627,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M24">
-        <v>1.4108248</v>
+        <v>1.4749532</v>
       </c>
       <c r="N24">
-        <v>14.2126445877551</v>
+        <v>14.1485161877551</v>
       </c>
       <c r="O24">
-        <v>2.131896688163265</v>
+        <v>2.122277428163265</v>
       </c>
       <c r="P24">
-        <v>12.08074789959184</v>
+        <v>12.02623875959184</v>
       </c>
       <c r="Q24">
-        <v>15.13074789959184</v>
+        <v>15.07623875959183</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2324170930505383</v>
+        <v>0.2345474537737948</v>
       </c>
       <c r="T24">
-        <v>1.141326910120259</v>
+        <v>1.154355931106334</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.07399684762778</v>
+        <v>10.59251872381788</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3673,22 +3673,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.190728439405822</v>
+        <v>0.1904849462322241</v>
       </c>
       <c r="C25">
-        <v>108.5303260012907</v>
+        <v>107.5197125877555</v>
       </c>
       <c r="D25">
-        <v>135.1143260012907</v>
+        <v>135.3417125877556</v>
       </c>
       <c r="E25">
-        <v>4.173999999999999</v>
+        <v>5.412000000000003</v>
       </c>
       <c r="F25">
-        <v>28.474</v>
+        <v>29.712</v>
       </c>
       <c r="G25">
         <v>1.89</v>
@@ -3709,28 +3709,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M25">
-        <v>1.4749532</v>
+        <v>1.5390816</v>
       </c>
       <c r="N25">
-        <v>14.1485161877551</v>
+        <v>14.0843877877551</v>
       </c>
       <c r="O25">
-        <v>2.122277428163265</v>
+        <v>2.112658168163265</v>
       </c>
       <c r="P25">
-        <v>12.02623875959184</v>
+        <v>11.97172961959184</v>
       </c>
       <c r="Q25">
-        <v>15.07623875959183</v>
+        <v>15.02172961959184</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2345474537737948</v>
+        <v>0.2367338766213475</v>
       </c>
       <c r="T25">
-        <v>1.154355931106334</v>
+        <v>1.167727821065728</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.59251872381788</v>
+        <v>10.15116377699214</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3755,22 +3755,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1904849462322241</v>
+        <v>0.1906027030586263</v>
       </c>
       <c r="C26">
-        <v>107.5197125877555</v>
+        <v>106.1716496523439</v>
       </c>
       <c r="D26">
-        <v>135.3417125877556</v>
+        <v>135.2316496523439</v>
       </c>
       <c r="E26">
-        <v>5.411999999999999</v>
+        <v>6.649999999999999</v>
       </c>
       <c r="F26">
-        <v>29.712</v>
+        <v>30.95</v>
       </c>
       <c r="G26">
         <v>1.89</v>
@@ -3791,45 +3791,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M26">
-        <v>1.5390816</v>
+        <v>1.655825</v>
       </c>
       <c r="N26">
-        <v>14.0843877877551</v>
+        <v>13.9676443877551</v>
       </c>
       <c r="O26">
-        <v>2.112658168163265</v>
+        <v>2.095146658163265</v>
       </c>
       <c r="P26">
-        <v>11.97172961959184</v>
+        <v>11.87249772959184</v>
       </c>
       <c r="Q26">
-        <v>15.02172961959184</v>
+        <v>14.92249772959184</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2367338766213475</v>
+        <v>0.2389786040781683</v>
       </c>
       <c r="T26">
-        <v>1.167727821065728</v>
+        <v>1.181456294757372</v>
       </c>
       <c r="U26">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>10.15116377699214</v>
+        <v>9.435459295369439</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3837,22 +3837,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1906027030586263</v>
+        <v>0.1903736598850284</v>
       </c>
       <c r="C27">
-        <v>106.1716496523439</v>
+        <v>105.1478925941902</v>
       </c>
       <c r="D27">
-        <v>135.2316496523439</v>
+        <v>135.4458925941902</v>
       </c>
       <c r="E27">
-        <v>6.649999999999999</v>
+        <v>7.888000000000002</v>
       </c>
       <c r="F27">
-        <v>30.95</v>
+        <v>32.188</v>
       </c>
       <c r="G27">
         <v>1.89</v>
@@ -3873,28 +3873,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M27">
-        <v>1.655825</v>
+        <v>1.722058</v>
       </c>
       <c r="N27">
-        <v>13.9676443877551</v>
+        <v>13.9014113877551</v>
       </c>
       <c r="O27">
-        <v>2.095146658163265</v>
+        <v>2.085211708163265</v>
       </c>
       <c r="P27">
-        <v>11.87249772959184</v>
+        <v>11.81619967959184</v>
       </c>
       <c r="Q27">
-        <v>14.92249772959184</v>
+        <v>14.86619967959184</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2389786040781683</v>
+        <v>0.241283999844633</v>
       </c>
       <c r="T27">
-        <v>1.181456294757372</v>
+        <v>1.19555580827852</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.435459295369439</v>
+        <v>9.072557014778306</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3919,22 +3919,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1903736598850284</v>
+        <v>0.1901446167114305</v>
       </c>
       <c r="C28">
-        <v>105.1478925941902</v>
+        <v>104.1248154489343</v>
       </c>
       <c r="D28">
-        <v>135.4458925941902</v>
+        <v>135.6608154489344</v>
       </c>
       <c r="E28">
-        <v>7.888000000000002</v>
+        <v>9.126000000000001</v>
       </c>
       <c r="F28">
-        <v>32.188</v>
+        <v>33.426</v>
       </c>
       <c r="G28">
         <v>1.89</v>
@@ -3955,28 +3955,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M28">
-        <v>1.722058</v>
+        <v>1.788291</v>
       </c>
       <c r="N28">
-        <v>13.9014113877551</v>
+        <v>13.8351783877551</v>
       </c>
       <c r="O28">
-        <v>2.085211708163265</v>
+        <v>2.075276758163265</v>
       </c>
       <c r="P28">
-        <v>11.81619967959184</v>
+        <v>11.75990162959184</v>
       </c>
       <c r="Q28">
-        <v>14.86619967959184</v>
+        <v>14.80990162959183</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.241283999844633</v>
+        <v>0.243652557138946</v>
       </c>
       <c r="T28">
-        <v>1.19555580827852</v>
+        <v>1.210041609841343</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.072557014778306</v>
+        <v>8.736536384601331</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4001,22 +4001,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1901446167114305</v>
+        <v>0.1899155735378327</v>
       </c>
       <c r="C29">
-        <v>104.1248154489343</v>
+        <v>103.1024214583372</v>
       </c>
       <c r="D29">
-        <v>135.6608154489344</v>
+        <v>135.8764214583372</v>
       </c>
       <c r="E29">
-        <v>9.126000000000001</v>
+        <v>10.364</v>
       </c>
       <c r="F29">
-        <v>33.426</v>
+        <v>34.664</v>
       </c>
       <c r="G29">
         <v>1.89</v>
@@ -4037,28 +4037,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M29">
-        <v>1.788291</v>
+        <v>1.854524</v>
       </c>
       <c r="N29">
-        <v>13.8351783877551</v>
+        <v>13.7689453877551</v>
       </c>
       <c r="O29">
-        <v>2.075276758163265</v>
+        <v>2.065341808163265</v>
       </c>
       <c r="P29">
-        <v>11.75990162959184</v>
+        <v>11.70360357959184</v>
       </c>
       <c r="Q29">
-        <v>14.80990162959183</v>
+        <v>14.75360357959184</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.243652557138946</v>
+        <v>0.2460869076914343</v>
       </c>
       <c r="T29">
-        <v>1.210041609841343</v>
+        <v>1.224929794780912</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.736536384601331</v>
+        <v>8.424517228008426</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1899155735378327</v>
+        <v>0.1896865303642348</v>
       </c>
       <c r="C30">
-        <v>103.1024214583372</v>
+        <v>102.080713884801</v>
       </c>
       <c r="D30">
-        <v>135.8764214583372</v>
+        <v>136.092713884801</v>
       </c>
       <c r="E30">
-        <v>10.364</v>
+        <v>11.602</v>
       </c>
       <c r="F30">
-        <v>34.664</v>
+        <v>35.902</v>
       </c>
       <c r="G30">
         <v>1.89</v>
@@ -4119,28 +4119,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M30">
-        <v>1.854524</v>
+        <v>1.920757</v>
       </c>
       <c r="N30">
-        <v>13.7689453877551</v>
+        <v>13.7027123877551</v>
       </c>
       <c r="O30">
-        <v>2.065341808163265</v>
+        <v>2.055406858163265</v>
       </c>
       <c r="P30">
-        <v>11.70360357959184</v>
+        <v>11.64730552959184</v>
       </c>
       <c r="Q30">
-        <v>14.75360357959184</v>
+        <v>14.69730552959184</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2460869076914343</v>
+        <v>0.2485898314989223</v>
       </c>
       <c r="T30">
-        <v>1.224929794780912</v>
+        <v>1.240237365211736</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.424517228008426</v>
+        <v>8.134016633939172</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4165,22 +4165,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1896865303642348</v>
+        <v>0.189457487190637</v>
       </c>
       <c r="C31">
-        <v>102.080713884801</v>
+        <v>101.0596960115338</v>
       </c>
       <c r="D31">
-        <v>136.092713884801</v>
+        <v>136.3096960115338</v>
       </c>
       <c r="E31">
-        <v>11.60199999999999</v>
+        <v>12.84</v>
       </c>
       <c r="F31">
-        <v>35.90199999999999</v>
+        <v>37.14</v>
       </c>
       <c r="G31">
         <v>1.89</v>
@@ -4201,28 +4201,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M31">
-        <v>1.920757</v>
+        <v>1.98699</v>
       </c>
       <c r="N31">
-        <v>13.7027123877551</v>
+        <v>13.6364793877551</v>
       </c>
       <c r="O31">
-        <v>2.055406858163265</v>
+        <v>2.045471908163265</v>
       </c>
       <c r="P31">
-        <v>11.64730552959184</v>
+        <v>11.59100747959184</v>
       </c>
       <c r="Q31">
-        <v>14.69730552959184</v>
+        <v>14.64100747959183</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2485898314989223</v>
+        <v>0.2511642674151957</v>
       </c>
       <c r="T31">
-        <v>1.240237365211736</v>
+        <v>1.255982294797726</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.134016633939172</v>
+        <v>7.862882746141199</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4247,22 +4247,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.189457487190637</v>
+        <v>0.1894392440170391</v>
       </c>
       <c r="C32">
-        <v>101.0596960115338</v>
+        <v>99.83900828203782</v>
       </c>
       <c r="D32">
-        <v>136.3096960115338</v>
+        <v>136.3270082820378</v>
       </c>
       <c r="E32">
-        <v>12.84</v>
+        <v>14.078</v>
       </c>
       <c r="F32">
-        <v>37.14</v>
+        <v>38.378</v>
       </c>
       <c r="G32">
         <v>1.89</v>
@@ -4283,45 +4283,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M32">
-        <v>1.98699</v>
+        <v>2.0839254</v>
       </c>
       <c r="N32">
-        <v>13.6364793877551</v>
+        <v>13.5395439877551</v>
       </c>
       <c r="O32">
-        <v>2.045471908163265</v>
+        <v>2.030931598163265</v>
       </c>
       <c r="P32">
-        <v>11.59100747959184</v>
+        <v>11.50861238959184</v>
       </c>
       <c r="Q32">
-        <v>14.64100747959183</v>
+        <v>14.55861238959184</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2511642674151957</v>
+        <v>0.2538133246623756</v>
       </c>
       <c r="T32">
-        <v>1.255982294797726</v>
+        <v>1.272183599154324</v>
       </c>
       <c r="U32">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y32">
-        <v>7.862882746141199</v>
+        <v>7.49713468042335</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4329,22 +4329,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1894392440170391</v>
+        <v>0.1892170008434412</v>
       </c>
       <c r="C33">
-        <v>99.83900828203782</v>
+        <v>98.81226459606977</v>
       </c>
       <c r="D33">
-        <v>136.3270082820378</v>
+        <v>136.5382645960698</v>
       </c>
       <c r="E33">
-        <v>14.078</v>
+        <v>15.316</v>
       </c>
       <c r="F33">
-        <v>38.378</v>
+        <v>39.616</v>
       </c>
       <c r="G33">
         <v>1.89</v>
@@ -4365,28 +4365,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M33">
-        <v>2.0839254</v>
+        <v>2.1511488</v>
       </c>
       <c r="N33">
-        <v>13.5395439877551</v>
+        <v>13.4723205877551</v>
       </c>
       <c r="O33">
-        <v>2.030931598163265</v>
+        <v>2.020848088163265</v>
       </c>
       <c r="P33">
-        <v>11.50861238959184</v>
+        <v>11.45147249959184</v>
       </c>
       <c r="Q33">
-        <v>14.55861238959184</v>
+        <v>14.50147249959184</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2538133246623756</v>
+        <v>0.2565402953580018</v>
       </c>
       <c r="T33">
-        <v>1.272183599154324</v>
+        <v>1.288861412462587</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.49713468042335</v>
+        <v>7.26284922166012</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4411,22 +4411,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1892170008434412</v>
+        <v>0.1889947576698434</v>
       </c>
       <c r="C34">
-        <v>98.81226459606977</v>
+        <v>97.7861766641871</v>
       </c>
       <c r="D34">
-        <v>136.5382645960698</v>
+        <v>136.7501766641871</v>
       </c>
       <c r="E34">
-        <v>15.316</v>
+        <v>16.554</v>
       </c>
       <c r="F34">
-        <v>39.616</v>
+        <v>40.854</v>
       </c>
       <c r="G34">
         <v>1.89</v>
@@ -4447,28 +4447,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M34">
-        <v>2.1511488</v>
+        <v>2.2183722</v>
       </c>
       <c r="N34">
-        <v>13.4723205877551</v>
+        <v>13.4050971877551</v>
       </c>
       <c r="O34">
-        <v>2.020848088163265</v>
+        <v>2.010764578163265</v>
       </c>
       <c r="P34">
-        <v>11.45147249959184</v>
+        <v>11.39433260959184</v>
       </c>
       <c r="Q34">
-        <v>14.50147249959184</v>
+        <v>14.44433260959184</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2565402953580018</v>
+        <v>0.2593486681639454</v>
       </c>
       <c r="T34">
-        <v>1.288861412462587</v>
+        <v>1.306037070944232</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.26284922166012</v>
+        <v>7.042762881609812</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4493,22 +4493,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1889947576698434</v>
+        <v>0.1887725144962455</v>
       </c>
       <c r="C35">
-        <v>97.7861766641871</v>
+        <v>96.76074754439439</v>
       </c>
       <c r="D35">
-        <v>136.7501766641871</v>
+        <v>136.9627475443944</v>
       </c>
       <c r="E35">
-        <v>16.554</v>
+        <v>17.792</v>
       </c>
       <c r="F35">
-        <v>40.854</v>
+        <v>42.092</v>
       </c>
       <c r="G35">
         <v>1.89</v>
@@ -4529,28 +4529,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M35">
-        <v>2.2183722</v>
+        <v>2.2855956</v>
       </c>
       <c r="N35">
-        <v>13.4050971877551</v>
+        <v>13.3378737877551</v>
       </c>
       <c r="O35">
-        <v>2.010764578163265</v>
+        <v>2.000681068163265</v>
       </c>
       <c r="P35">
-        <v>11.39433260959184</v>
+        <v>11.33719271959183</v>
       </c>
       <c r="Q35">
-        <v>14.44433260959184</v>
+        <v>14.38719271959183</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2593486681639454</v>
+        <v>0.2622421431761296</v>
       </c>
       <c r="T35">
-        <v>1.306037070944232</v>
+        <v>1.32373320392532</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.042762881609812</v>
+        <v>6.835622796856582</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4575,22 +4575,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1887725144962455</v>
+        <v>0.1885502713226477</v>
       </c>
       <c r="C36">
-        <v>96.76074754439439</v>
+        <v>95.73598031373984</v>
       </c>
       <c r="D36">
-        <v>136.9627475443944</v>
+        <v>137.1759803137399</v>
       </c>
       <c r="E36">
-        <v>17.792</v>
+        <v>19.03</v>
       </c>
       <c r="F36">
-        <v>42.092</v>
+        <v>43.33000000000001</v>
       </c>
       <c r="G36">
         <v>1.89</v>
@@ -4611,28 +4611,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M36">
-        <v>2.2855956</v>
+        <v>2.352819</v>
       </c>
       <c r="N36">
-        <v>13.3378737877551</v>
+        <v>13.2706503877551</v>
       </c>
       <c r="O36">
-        <v>2.000681068163265</v>
+        <v>1.990597558163265</v>
       </c>
       <c r="P36">
-        <v>11.33719271959183</v>
+        <v>11.28005282959183</v>
       </c>
       <c r="Q36">
-        <v>14.38719271959183</v>
+        <v>14.33005282959184</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2622421431761296</v>
+        <v>0.2652246481886887</v>
       </c>
       <c r="T36">
-        <v>1.32373320392532</v>
+        <v>1.341973833305826</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.835622796856582</v>
+        <v>6.640319288374966</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4657,22 +4657,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1885502713226477</v>
+        <v>0.1883280281490498</v>
       </c>
       <c r="C37">
-        <v>95.73598031373984</v>
+        <v>94.71187806846388</v>
       </c>
       <c r="D37">
-        <v>137.1759803137399</v>
+        <v>137.3898780684639</v>
       </c>
       <c r="E37">
-        <v>19.03</v>
+        <v>20.268</v>
       </c>
       <c r="F37">
-        <v>43.33000000000001</v>
+        <v>44.568</v>
       </c>
       <c r="G37">
         <v>1.89</v>
@@ -4693,28 +4693,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M37">
-        <v>2.352819</v>
+        <v>2.4200424</v>
       </c>
       <c r="N37">
-        <v>13.2706503877551</v>
+        <v>13.2034269877551</v>
       </c>
       <c r="O37">
-        <v>1.990597558163265</v>
+        <v>1.980514048163265</v>
       </c>
       <c r="P37">
-        <v>11.28005282959183</v>
+        <v>11.22291293959184</v>
       </c>
       <c r="Q37">
-        <v>14.33005282959184</v>
+        <v>14.27291293959184</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2652246481886887</v>
+        <v>0.2683003564828904</v>
       </c>
       <c r="T37">
-        <v>1.341973833305826</v>
+        <v>1.360784482354473</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.640319288374966</v>
+        <v>6.455865974808995</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4739,22 +4739,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1883280281490498</v>
+        <v>0.1881057849754519</v>
       </c>
       <c r="C38">
-        <v>94.71187806846389</v>
+        <v>93.6884439241487</v>
       </c>
       <c r="D38">
-        <v>137.3898780684639</v>
+        <v>137.6044439241487</v>
       </c>
       <c r="E38">
-        <v>20.268</v>
+        <v>21.506</v>
       </c>
       <c r="F38">
-        <v>44.568</v>
+        <v>45.806</v>
       </c>
       <c r="G38">
         <v>1.89</v>
@@ -4775,28 +4775,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M38">
-        <v>2.4200424</v>
+        <v>2.4872658</v>
       </c>
       <c r="N38">
-        <v>13.2034269877551</v>
+        <v>13.1362035877551</v>
       </c>
       <c r="O38">
-        <v>1.980514048163265</v>
+        <v>1.970430538163265</v>
       </c>
       <c r="P38">
-        <v>11.22291293959184</v>
+        <v>11.16577304959184</v>
       </c>
       <c r="Q38">
-        <v>14.27291293959184</v>
+        <v>14.21577304959184</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2683003564828903</v>
+        <v>0.2714737063102412</v>
       </c>
       <c r="T38">
-        <v>1.360784482354473</v>
+        <v>1.380192294864982</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.455865974808996</v>
+        <v>6.281383110624969</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4821,22 +4821,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1881057849754519</v>
+        <v>0.1878835418018541</v>
       </c>
       <c r="C39">
-        <v>93.6884439241487</v>
+        <v>92.66568101586985</v>
       </c>
       <c r="D39">
-        <v>137.6044439241487</v>
+        <v>137.8196810158699</v>
       </c>
       <c r="E39">
-        <v>21.506</v>
+        <v>22.744</v>
       </c>
       <c r="F39">
-        <v>45.806</v>
+        <v>47.044</v>
       </c>
       <c r="G39">
         <v>1.89</v>
@@ -4857,28 +4857,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M39">
-        <v>2.4872658</v>
+        <v>2.5544892</v>
       </c>
       <c r="N39">
-        <v>13.1362035877551</v>
+        <v>13.0689801877551</v>
       </c>
       <c r="O39">
-        <v>1.970430538163265</v>
+        <v>1.960347028163265</v>
       </c>
       <c r="P39">
-        <v>11.16577304959184</v>
+        <v>11.10863315959184</v>
       </c>
       <c r="Q39">
-        <v>14.21577304959184</v>
+        <v>14.15863315959184</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2714737063102412</v>
+        <v>0.274749422261055</v>
       </c>
       <c r="T39">
-        <v>1.380192294864982</v>
+        <v>1.400226165843572</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.281383110624969</v>
+        <v>6.116083555082207</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4903,22 +4903,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1878835418018541</v>
+        <v>0.1879927986282562</v>
       </c>
       <c r="C40">
-        <v>92.66568101586985</v>
+        <v>91.32178436632913</v>
       </c>
       <c r="D40">
-        <v>137.8196810158699</v>
+        <v>137.7137843663292</v>
       </c>
       <c r="E40">
-        <v>22.744</v>
+        <v>23.982</v>
       </c>
       <c r="F40">
-        <v>47.044</v>
+        <v>48.282</v>
       </c>
       <c r="G40">
         <v>1.89</v>
@@ -4939,45 +4939,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M40">
-        <v>2.5544892</v>
+        <v>2.6699946</v>
       </c>
       <c r="N40">
-        <v>13.0689801877551</v>
+        <v>12.9534747877551</v>
       </c>
       <c r="O40">
-        <v>1.960347028163265</v>
+        <v>1.943021218163265</v>
       </c>
       <c r="P40">
-        <v>11.10863315959184</v>
+        <v>11.01045356959184</v>
       </c>
       <c r="Q40">
-        <v>14.15863315959184</v>
+        <v>14.06045356959184</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.274749422261055</v>
+        <v>0.2781325387348463</v>
       </c>
       <c r="T40">
-        <v>1.400226165843572</v>
+        <v>1.420916885050967</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.116083555082207</v>
+        <v>5.851498496571903</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4985,22 +4985,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1879927986282562</v>
+        <v>0.1877790554546584</v>
       </c>
       <c r="C41">
-        <v>91.32178436632913</v>
+        <v>90.29110636339669</v>
       </c>
       <c r="D41">
-        <v>137.7137843663292</v>
+        <v>137.9211063633967</v>
       </c>
       <c r="E41">
-        <v>23.982</v>
+        <v>25.22</v>
       </c>
       <c r="F41">
-        <v>48.282</v>
+        <v>49.52</v>
       </c>
       <c r="G41">
         <v>1.89</v>
@@ -5021,28 +5021,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M41">
-        <v>2.6699946</v>
+        <v>2.738456</v>
       </c>
       <c r="N41">
-        <v>12.9534747877551</v>
+        <v>12.8850133877551</v>
       </c>
       <c r="O41">
-        <v>1.943021218163265</v>
+        <v>1.932752008163265</v>
       </c>
       <c r="P41">
-        <v>11.01045356959184</v>
+        <v>10.95226137959184</v>
       </c>
       <c r="Q41">
-        <v>14.06045356959184</v>
+        <v>14.00226137959184</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2781325387348463</v>
+        <v>0.281628425757764</v>
       </c>
       <c r="T41">
-        <v>1.420916885050967</v>
+        <v>1.44229729489861</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.851498496571903</v>
+        <v>5.705211034157606</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5067,22 +5067,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1877790554546584</v>
+        <v>0.1875653122810605</v>
       </c>
       <c r="C42">
-        <v>90.29110636339669</v>
+        <v>89.26105352977967</v>
       </c>
       <c r="D42">
-        <v>137.9211063633967</v>
+        <v>138.1290535297797</v>
       </c>
       <c r="E42">
-        <v>25.22</v>
+        <v>26.458</v>
       </c>
       <c r="F42">
-        <v>49.52</v>
+        <v>50.758</v>
       </c>
       <c r="G42">
         <v>1.89</v>
@@ -5103,28 +5103,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M42">
-        <v>2.738456</v>
+        <v>2.8069174</v>
       </c>
       <c r="N42">
-        <v>12.8850133877551</v>
+        <v>12.8165519877551</v>
       </c>
       <c r="O42">
-        <v>1.932752008163265</v>
+        <v>1.922482798163265</v>
       </c>
       <c r="P42">
-        <v>10.95226137959184</v>
+        <v>10.89406918959184</v>
       </c>
       <c r="Q42">
-        <v>14.00226137959184</v>
+        <v>13.94406918959184</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.281628425757764</v>
+        <v>0.2852428174255263</v>
       </c>
       <c r="T42">
-        <v>1.44229729489861</v>
+        <v>1.464402464402105</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.705211034157606</v>
+        <v>5.566059545519615</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1875653122810605</v>
+        <v>0.1873515691074627</v>
       </c>
       <c r="C43">
-        <v>89.26105352977967</v>
+        <v>88.23162869749899</v>
       </c>
       <c r="D43">
-        <v>138.1290535297797</v>
+        <v>138.337628697499</v>
       </c>
       <c r="E43">
-        <v>26.458</v>
+        <v>27.696</v>
       </c>
       <c r="F43">
-        <v>50.758</v>
+        <v>51.996</v>
       </c>
       <c r="G43">
         <v>1.89</v>
@@ -5185,28 +5185,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M43">
-        <v>2.8069174</v>
+        <v>2.8753788</v>
       </c>
       <c r="N43">
-        <v>12.8165519877551</v>
+        <v>12.7480905877551</v>
       </c>
       <c r="O43">
-        <v>1.922482798163265</v>
+        <v>1.912213588163265</v>
       </c>
       <c r="P43">
-        <v>10.89406918959184</v>
+        <v>10.83587699959184</v>
       </c>
       <c r="Q43">
-        <v>13.94406918959184</v>
+        <v>13.88587699959184</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2852428174255263</v>
+        <v>0.2889818432887287</v>
       </c>
       <c r="T43">
-        <v>1.464402464402105</v>
+        <v>1.487269881129858</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.566059545519615</v>
+        <v>5.433534318245339</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5231,22 +5231,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1873515691074626</v>
+        <v>0.1871378259338648</v>
       </c>
       <c r="C44">
-        <v>88.23162869749903</v>
+        <v>87.20283471570706</v>
       </c>
       <c r="D44">
-        <v>138.337628697499</v>
+        <v>138.5468347157071</v>
       </c>
       <c r="E44">
-        <v>27.69599999999999</v>
+        <v>28.93399999999999</v>
       </c>
       <c r="F44">
-        <v>51.996</v>
+        <v>53.23399999999999</v>
       </c>
       <c r="G44">
         <v>1.89</v>
@@ -5267,28 +5267,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M44">
-        <v>2.8753788</v>
+        <v>2.9438402</v>
       </c>
       <c r="N44">
-        <v>12.7480905877551</v>
+        <v>12.6796291877551</v>
       </c>
       <c r="O44">
-        <v>1.912213588163265</v>
+        <v>1.901944378163265</v>
       </c>
       <c r="P44">
-        <v>10.83587699959184</v>
+        <v>10.77768480959184</v>
       </c>
       <c r="Q44">
-        <v>13.88587699959184</v>
+        <v>13.82768480959184</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2889818432887287</v>
+        <v>0.2928520630418681</v>
       </c>
       <c r="T44">
-        <v>1.487269881129858</v>
+        <v>1.51093966335683</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.433534318245339</v>
+        <v>5.307173055030331</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5313,22 +5313,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1871378259338648</v>
+        <v>0.186924082760267</v>
       </c>
       <c r="C45">
-        <v>87.20283471570706</v>
+        <v>86.17467445081715</v>
       </c>
       <c r="D45">
-        <v>138.5468347157071</v>
+        <v>138.7566744508172</v>
       </c>
       <c r="E45">
-        <v>28.93399999999999</v>
+        <v>30.172</v>
       </c>
       <c r="F45">
-        <v>53.23399999999999</v>
+        <v>54.472</v>
       </c>
       <c r="G45">
         <v>1.89</v>
@@ -5349,28 +5349,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M45">
-        <v>2.9438402</v>
+        <v>3.0123016</v>
       </c>
       <c r="N45">
-        <v>12.6796291877551</v>
+        <v>12.6111677877551</v>
       </c>
       <c r="O45">
-        <v>1.901944378163265</v>
+        <v>1.891675168163265</v>
       </c>
       <c r="P45">
-        <v>10.77768480959184</v>
+        <v>10.71949261959184</v>
       </c>
       <c r="Q45">
-        <v>13.82768480959184</v>
+        <v>13.76949261959184</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2928520630418681</v>
+        <v>0.2968605049290481</v>
       </c>
       <c r="T45">
-        <v>1.51093966335683</v>
+        <v>1.535454794949052</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.307173055030331</v>
+        <v>5.186555485597823</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5395,22 +5395,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.186924082760267</v>
+        <v>0.1867103395866691</v>
       </c>
       <c r="C46">
-        <v>86.17467445081715</v>
+        <v>85.14715078663465</v>
       </c>
       <c r="D46">
-        <v>138.7566744508172</v>
+        <v>138.9671507866347</v>
       </c>
       <c r="E46">
-        <v>30.172</v>
+        <v>31.41</v>
       </c>
       <c r="F46">
-        <v>54.472</v>
+        <v>55.71</v>
       </c>
       <c r="G46">
         <v>1.89</v>
@@ -5431,28 +5431,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M46">
-        <v>3.0123016</v>
+        <v>3.080763</v>
       </c>
       <c r="N46">
-        <v>12.6111677877551</v>
+        <v>12.5427063877551</v>
       </c>
       <c r="O46">
-        <v>1.891675168163265</v>
+        <v>1.881405958163265</v>
       </c>
       <c r="P46">
-        <v>10.71949261959184</v>
+        <v>10.66130042959183</v>
       </c>
       <c r="Q46">
-        <v>13.76949261959184</v>
+        <v>13.71130042959183</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2968605049290481</v>
+        <v>0.3010147083393983</v>
       </c>
       <c r="T46">
-        <v>1.535454794949052</v>
+        <v>1.5608613858719</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.186555485597823</v>
+        <v>5.071298697028983</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5477,22 +5477,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1867103395866691</v>
+        <v>0.1864965964130713</v>
       </c>
       <c r="C47">
-        <v>85.14715078663465</v>
+        <v>84.12026662448889</v>
       </c>
       <c r="D47">
-        <v>138.9671507866347</v>
+        <v>139.1782666244889</v>
       </c>
       <c r="E47">
-        <v>31.41</v>
+        <v>32.648</v>
       </c>
       <c r="F47">
-        <v>55.71</v>
+        <v>56.948</v>
       </c>
       <c r="G47">
         <v>1.89</v>
@@ -5513,28 +5513,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M47">
-        <v>3.080763</v>
+        <v>3.1492244</v>
       </c>
       <c r="N47">
-        <v>12.5427063877551</v>
+        <v>12.4742449877551</v>
       </c>
       <c r="O47">
-        <v>1.881405958163265</v>
+        <v>1.871136748163265</v>
       </c>
       <c r="P47">
-        <v>10.66130042959183</v>
+        <v>10.60310823959184</v>
       </c>
       <c r="Q47">
-        <v>13.71130042959183</v>
+        <v>13.65310823959184</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3010147083393983</v>
+        <v>0.3053227711353171</v>
       </c>
       <c r="T47">
-        <v>1.5608613858719</v>
+        <v>1.587208961643742</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.071298697028983</v>
+        <v>4.961053073180527</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5559,22 +5559,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1864965964130713</v>
+        <v>0.1862828532394734</v>
       </c>
       <c r="C48">
-        <v>84.12026662448889</v>
+        <v>83.09402488336664</v>
       </c>
       <c r="D48">
-        <v>139.1782666244889</v>
+        <v>139.3900248833667</v>
       </c>
       <c r="E48">
-        <v>32.648</v>
+        <v>33.886</v>
       </c>
       <c r="F48">
-        <v>56.948</v>
+        <v>58.186</v>
       </c>
       <c r="G48">
         <v>1.89</v>
@@ -5595,28 +5595,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M48">
-        <v>3.1492244</v>
+        <v>3.2176858</v>
       </c>
       <c r="N48">
-        <v>12.4742449877551</v>
+        <v>12.4057835877551</v>
       </c>
       <c r="O48">
-        <v>1.871136748163265</v>
+        <v>1.860867538163265</v>
       </c>
       <c r="P48">
-        <v>10.60310823959184</v>
+        <v>10.54491604959184</v>
       </c>
       <c r="Q48">
-        <v>13.65310823959184</v>
+        <v>13.59491604959183</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3053227711353171</v>
+        <v>0.309793402338629</v>
       </c>
       <c r="T48">
-        <v>1.587208961643742</v>
+        <v>1.614550785557918</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.961053073180527</v>
+        <v>4.855498752474558</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5641,22 +5641,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1862828532394734</v>
+        <v>0.1860691100658755</v>
       </c>
       <c r="C49">
-        <v>83.09402488336664</v>
+        <v>82.06842850004648</v>
       </c>
       <c r="D49">
-        <v>139.3900248833667</v>
+        <v>139.6024285000465</v>
       </c>
       <c r="E49">
-        <v>33.886</v>
+        <v>35.12400000000001</v>
       </c>
       <c r="F49">
-        <v>58.186</v>
+        <v>59.42400000000001</v>
       </c>
       <c r="G49">
         <v>1.89</v>
@@ -5677,28 +5677,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M49">
-        <v>3.2176858</v>
+        <v>3.2861472</v>
       </c>
       <c r="N49">
-        <v>12.4057835877551</v>
+        <v>12.3373221877551</v>
       </c>
       <c r="O49">
-        <v>1.860867538163265</v>
+        <v>1.850598328163265</v>
       </c>
       <c r="P49">
-        <v>10.54491604959184</v>
+        <v>10.48672385959184</v>
       </c>
       <c r="Q49">
-        <v>13.59491604959183</v>
+        <v>13.53672385959183</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.309793402338629</v>
+        <v>0.3144359808959145</v>
       </c>
       <c r="T49">
-        <v>1.614550785557918</v>
+        <v>1.642944218084178</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.855498752474558</v>
+        <v>4.754342528464671</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5723,22 +5723,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1860691100658755</v>
+        <v>0.1858553668922776</v>
       </c>
       <c r="C50">
-        <v>82.06842850004648</v>
+        <v>81.04348042923479</v>
       </c>
       <c r="D50">
-        <v>139.6024285000465</v>
+        <v>139.8154804292348</v>
       </c>
       <c r="E50">
-        <v>35.124</v>
+        <v>36.36199999999999</v>
       </c>
       <c r="F50">
-        <v>59.424</v>
+        <v>60.662</v>
       </c>
       <c r="G50">
         <v>1.89</v>
@@ -5759,28 +5759,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M50">
-        <v>3.2861472</v>
+        <v>3.3546086</v>
       </c>
       <c r="N50">
-        <v>12.3373221877551</v>
+        <v>12.2688607877551</v>
       </c>
       <c r="O50">
-        <v>1.850598328163265</v>
+        <v>1.840329118163265</v>
       </c>
       <c r="P50">
-        <v>10.48672385959184</v>
+        <v>10.42853166959184</v>
       </c>
       <c r="Q50">
-        <v>13.53672385959183</v>
+        <v>13.47853166959183</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3144359808959145</v>
+        <v>0.3192606213574071</v>
       </c>
       <c r="T50">
-        <v>1.642944218084178</v>
+        <v>1.672451118552643</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.754342528464671</v>
+        <v>4.657315129924577</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5805,22 +5805,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1858553668922776</v>
+        <v>0.1856416237186798</v>
       </c>
       <c r="C51">
-        <v>81.04348042923479</v>
+        <v>80.01918364370238</v>
       </c>
       <c r="D51">
-        <v>139.8154804292348</v>
+        <v>140.0291836437024</v>
       </c>
       <c r="E51">
-        <v>36.36199999999999</v>
+        <v>37.59999999999999</v>
       </c>
       <c r="F51">
-        <v>60.662</v>
+        <v>61.9</v>
       </c>
       <c r="G51">
         <v>1.89</v>
@@ -5841,28 +5841,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M51">
-        <v>3.3546086</v>
+        <v>3.42307</v>
       </c>
       <c r="N51">
-        <v>12.2688607877551</v>
+        <v>12.2003993877551</v>
       </c>
       <c r="O51">
-        <v>1.840329118163265</v>
+        <v>1.830059908163265</v>
       </c>
       <c r="P51">
-        <v>10.42853166959184</v>
+        <v>10.37033947959184</v>
       </c>
       <c r="Q51">
-        <v>13.47853166959183</v>
+        <v>13.42033947959183</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3192606213574071</v>
+        <v>0.3242782474373596</v>
       </c>
       <c r="T51">
-        <v>1.672451118552643</v>
+        <v>1.703138295039848</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.657315129924577</v>
+        <v>4.564168827326085</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5887,22 +5887,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1856416237186798</v>
+        <v>0.1865116305450819</v>
       </c>
       <c r="C52">
-        <v>80.01918364370238</v>
+        <v>77.91539632254339</v>
       </c>
       <c r="D52">
-        <v>140.0291836437024</v>
+        <v>139.1633963225434</v>
       </c>
       <c r="E52">
-        <v>37.59999999999999</v>
+        <v>38.83799999999999</v>
       </c>
       <c r="F52">
-        <v>61.9</v>
+        <v>63.138</v>
       </c>
       <c r="G52">
         <v>1.89</v>
@@ -5923,45 +5923,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M52">
-        <v>3.42307</v>
+        <v>3.6493764</v>
       </c>
       <c r="N52">
-        <v>12.2003993877551</v>
+        <v>11.9740929877551</v>
       </c>
       <c r="O52">
-        <v>1.830059908163265</v>
+        <v>1.796113948163265</v>
       </c>
       <c r="P52">
-        <v>10.37033947959184</v>
+        <v>10.17797903959184</v>
       </c>
       <c r="Q52">
-        <v>13.42033947959183</v>
+        <v>13.22797903959184</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3242782474373596</v>
+        <v>0.3295006745817999</v>
       </c>
       <c r="T52">
-        <v>1.703138295039848</v>
+        <v>1.735078009342857</v>
       </c>
       <c r="U52">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V52">
         <v>0.15</v>
       </c>
       <c r="W52">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.564168827326085</v>
+        <v>4.281134000799453</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5969,22 +5969,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1865116305450819</v>
+        <v>0.1863191373714841</v>
       </c>
       <c r="C53">
-        <v>77.91539632254339</v>
+        <v>76.8680323050001</v>
       </c>
       <c r="D53">
-        <v>139.1633963225434</v>
+        <v>139.3540323050001</v>
       </c>
       <c r="E53">
-        <v>38.83799999999999</v>
+        <v>40.07600000000001</v>
       </c>
       <c r="F53">
-        <v>63.138</v>
+        <v>64.376</v>
       </c>
       <c r="G53">
         <v>1.89</v>
@@ -6005,28 +6005,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M53">
-        <v>3.6493764</v>
+        <v>3.7209328</v>
       </c>
       <c r="N53">
-        <v>11.9740929877551</v>
+        <v>11.9025365877551</v>
       </c>
       <c r="O53">
-        <v>1.796113948163265</v>
+        <v>1.785380488163265</v>
       </c>
       <c r="P53">
-        <v>10.17797903959184</v>
+        <v>10.11715609959184</v>
       </c>
       <c r="Q53">
-        <v>13.22797903959184</v>
+        <v>13.16715609959184</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3295006745817999</v>
+        <v>0.3349407028572585</v>
       </c>
       <c r="T53">
-        <v>1.735078009342857</v>
+        <v>1.768348545075157</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.281134000799453</v>
+        <v>4.198804500784078</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6051,22 +6051,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1863191373714841</v>
+        <v>0.1861266441978862</v>
       </c>
       <c r="C54">
-        <v>76.8680323050001</v>
+        <v>75.82119129754486</v>
       </c>
       <c r="D54">
-        <v>139.3540323050001</v>
+        <v>139.5451912975449</v>
       </c>
       <c r="E54">
-        <v>40.07600000000001</v>
+        <v>41.31400000000001</v>
       </c>
       <c r="F54">
-        <v>64.376</v>
+        <v>65.614</v>
       </c>
       <c r="G54">
         <v>1.89</v>
@@ -6087,28 +6087,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M54">
-        <v>3.7209328</v>
+        <v>3.7924892</v>
       </c>
       <c r="N54">
-        <v>11.9025365877551</v>
+        <v>11.8309801877551</v>
       </c>
       <c r="O54">
-        <v>1.785380488163265</v>
+        <v>1.774647028163265</v>
       </c>
       <c r="P54">
-        <v>10.11715609959184</v>
+        <v>10.05633315959184</v>
       </c>
       <c r="Q54">
-        <v>13.16715609959184</v>
+        <v>13.10633315959183</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3349407028572585</v>
+        <v>0.3406122216976302</v>
       </c>
       <c r="T54">
-        <v>1.768348545075157</v>
+        <v>1.803034848285428</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.198804500784078</v>
+        <v>4.11958177435419</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6133,22 +6133,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1861266441978862</v>
+        <v>0.1859341510242884</v>
       </c>
       <c r="C55">
-        <v>75.82119129754486</v>
+        <v>74.77487545545239</v>
       </c>
       <c r="D55">
-        <v>139.5451912975449</v>
+        <v>139.7368754554524</v>
       </c>
       <c r="E55">
-        <v>41.31400000000001</v>
+        <v>42.55200000000001</v>
       </c>
       <c r="F55">
-        <v>65.614</v>
+        <v>66.852</v>
       </c>
       <c r="G55">
         <v>1.89</v>
@@ -6169,28 +6169,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M55">
-        <v>3.7924892</v>
+        <v>3.8640456</v>
       </c>
       <c r="N55">
-        <v>11.8309801877551</v>
+        <v>11.7594237877551</v>
       </c>
       <c r="O55">
-        <v>1.774647028163265</v>
+        <v>1.763913568163265</v>
       </c>
       <c r="P55">
-        <v>10.05633315959184</v>
+        <v>9.995510219591836</v>
       </c>
       <c r="Q55">
-        <v>13.10633315959183</v>
+        <v>13.04551021959184</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3406122216976302</v>
+        <v>0.3465303283136704</v>
       </c>
       <c r="T55">
-        <v>1.803034848285428</v>
+        <v>1.839229251635277</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.11958177435419</v>
+        <v>4.04329322297726</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1859341510242884</v>
+        <v>0.1873779078506905</v>
       </c>
       <c r="C56">
-        <v>74.77487545545239</v>
+        <v>72.11189276640408</v>
       </c>
       <c r="D56">
-        <v>139.7368754554524</v>
+        <v>138.3118927664041</v>
       </c>
       <c r="E56">
-        <v>42.55200000000001</v>
+        <v>43.79000000000001</v>
       </c>
       <c r="F56">
-        <v>66.852</v>
+        <v>68.09</v>
       </c>
       <c r="G56">
         <v>1.89</v>
@@ -6251,45 +6251,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M56">
-        <v>3.8640456</v>
+        <v>4.173917</v>
       </c>
       <c r="N56">
-        <v>11.7594237877551</v>
+        <v>11.4495523877551</v>
       </c>
       <c r="O56">
-        <v>1.763913568163265</v>
+        <v>1.717432858163265</v>
       </c>
       <c r="P56">
-        <v>9.995510219591836</v>
+        <v>9.732119529591836</v>
       </c>
       <c r="Q56">
-        <v>13.04551021959184</v>
+        <v>12.78211952959184</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3465303283136704</v>
+        <v>0.3527114618904234</v>
       </c>
       <c r="T56">
-        <v>1.839229251635277</v>
+        <v>1.877032295134007</v>
       </c>
       <c r="U56">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V56">
         <v>0.15</v>
       </c>
       <c r="W56">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.04329322297726</v>
+        <v>3.743119325984465</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6297,22 +6297,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1873779078506905</v>
+        <v>0.1872151646770926</v>
       </c>
       <c r="C57">
-        <v>72.11189276640408</v>
+        <v>71.03306463758585</v>
       </c>
       <c r="D57">
-        <v>138.3118927664041</v>
+        <v>138.4710646375859</v>
       </c>
       <c r="E57">
-        <v>43.79000000000001</v>
+        <v>45.02800000000001</v>
       </c>
       <c r="F57">
-        <v>68.09</v>
+        <v>69.328</v>
       </c>
       <c r="G57">
         <v>1.89</v>
@@ -6333,28 +6333,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M57">
-        <v>4.173917</v>
+        <v>4.2498064</v>
       </c>
       <c r="N57">
-        <v>11.4495523877551</v>
+        <v>11.3736629877551</v>
       </c>
       <c r="O57">
-        <v>1.717432858163265</v>
+        <v>1.706049448163265</v>
       </c>
       <c r="P57">
-        <v>9.732119529591836</v>
+        <v>9.667613539591835</v>
       </c>
       <c r="Q57">
-        <v>12.78211952959184</v>
+        <v>12.71761353959183</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3527114618904234</v>
+        <v>0.3591735560843015</v>
       </c>
       <c r="T57">
-        <v>1.877032295134007</v>
+        <v>1.91655365879177</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.743119325984465</v>
+        <v>3.676277909449028</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6379,22 +6379,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1872151646770926</v>
+        <v>0.1870524215034948</v>
       </c>
       <c r="C58">
-        <v>71.03306463758585</v>
+        <v>69.95460328669876</v>
       </c>
       <c r="D58">
-        <v>138.4710646375859</v>
+        <v>138.6306032866988</v>
       </c>
       <c r="E58">
-        <v>45.02800000000001</v>
+        <v>46.26600000000001</v>
       </c>
       <c r="F58">
-        <v>69.328</v>
+        <v>70.566</v>
       </c>
       <c r="G58">
         <v>1.89</v>
@@ -6415,28 +6415,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M58">
-        <v>4.2498064</v>
+        <v>4.3256958</v>
       </c>
       <c r="N58">
-        <v>11.3736629877551</v>
+        <v>11.2977735877551</v>
       </c>
       <c r="O58">
-        <v>1.706049448163265</v>
+        <v>1.694666038163265</v>
       </c>
       <c r="P58">
-        <v>9.667613539591835</v>
+        <v>9.603107549591837</v>
       </c>
       <c r="Q58">
-        <v>12.71761353959183</v>
+        <v>12.65310754959184</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3591735560843015</v>
+        <v>0.3659362127988251</v>
       </c>
       <c r="T58">
-        <v>1.91655365879177</v>
+        <v>1.95791322541036</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.676277909449028</v>
+        <v>3.611781805774484</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6461,22 +6461,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1870524215034948</v>
+        <v>0.1868896783298969</v>
       </c>
       <c r="C59">
-        <v>69.95460328669876</v>
+        <v>68.87650998294842</v>
       </c>
       <c r="D59">
-        <v>138.6306032866988</v>
+        <v>138.7905099829484</v>
       </c>
       <c r="E59">
-        <v>46.26600000000001</v>
+        <v>47.504</v>
       </c>
       <c r="F59">
-        <v>70.566</v>
+        <v>71.804</v>
       </c>
       <c r="G59">
         <v>1.89</v>
@@ -6497,28 +6497,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M59">
-        <v>4.3256958</v>
+        <v>4.4015852</v>
       </c>
       <c r="N59">
-        <v>11.2977735877551</v>
+        <v>11.2218841877551</v>
       </c>
       <c r="O59">
-        <v>1.694666038163265</v>
+        <v>1.683282628163265</v>
       </c>
       <c r="P59">
-        <v>9.603107549591837</v>
+        <v>9.538601559591836</v>
       </c>
       <c r="Q59">
-        <v>12.65310754959184</v>
+        <v>12.58860155959184</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3659362127988251</v>
+        <v>0.3730209007854689</v>
       </c>
       <c r="T59">
-        <v>1.95791322541036</v>
+        <v>2.001242295201263</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.611781805774484</v>
+        <v>3.549509705674924</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6543,22 +6543,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1868896783298969</v>
+        <v>0.188131135156299</v>
       </c>
       <c r="C60">
-        <v>68.87650998294846</v>
+        <v>66.42793560040768</v>
       </c>
       <c r="D60">
-        <v>138.7905099829485</v>
+        <v>137.5799356004077</v>
       </c>
       <c r="E60">
-        <v>47.50399999999999</v>
+        <v>48.74199999999999</v>
       </c>
       <c r="F60">
-        <v>71.80399999999999</v>
+        <v>73.04199999999999</v>
       </c>
       <c r="G60">
         <v>1.89</v>
@@ -6579,45 +6579,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M60">
-        <v>4.4015852</v>
+        <v>4.6819922</v>
       </c>
       <c r="N60">
-        <v>11.2218841877551</v>
+        <v>10.9414771877551</v>
       </c>
       <c r="O60">
-        <v>1.683282628163265</v>
+        <v>1.641221578163265</v>
       </c>
       <c r="P60">
-        <v>9.538601559591836</v>
+        <v>9.300255609591837</v>
       </c>
       <c r="Q60">
-        <v>12.58860155959184</v>
+        <v>12.35025560959184</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3730209007854688</v>
+        <v>0.3804511833080464</v>
       </c>
       <c r="T60">
-        <v>2.001242295201263</v>
+        <v>2.046684978152697</v>
       </c>
       <c r="U60">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V60">
         <v>0.15</v>
       </c>
       <c r="W60">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.549509705674924</v>
+        <v>3.336927683851139</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6625,22 +6625,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.188131135156299</v>
+        <v>0.1879921919827012</v>
       </c>
       <c r="C61">
-        <v>66.42793560040768</v>
+        <v>65.32437190530712</v>
       </c>
       <c r="D61">
-        <v>137.5799356004077</v>
+        <v>137.7143719053071</v>
       </c>
       <c r="E61">
-        <v>48.74199999999999</v>
+        <v>49.98</v>
       </c>
       <c r="F61">
-        <v>73.04199999999999</v>
+        <v>74.28</v>
       </c>
       <c r="G61">
         <v>1.89</v>
@@ -6661,28 +6661,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M61">
-        <v>4.6819922</v>
+        <v>4.761348000000001</v>
       </c>
       <c r="N61">
-        <v>10.9414771877551</v>
+        <v>10.8621213877551</v>
       </c>
       <c r="O61">
-        <v>1.641221578163265</v>
+        <v>1.629318208163265</v>
       </c>
       <c r="P61">
-        <v>9.300255609591837</v>
+        <v>9.232803179591833</v>
       </c>
       <c r="Q61">
-        <v>12.35025560959184</v>
+        <v>12.28280317959183</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3804511833080464</v>
+        <v>0.3882529799567529</v>
       </c>
       <c r="T61">
-        <v>2.046684978152697</v>
+        <v>2.094399795251704</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.336927683851139</v>
+        <v>3.28131222245362</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6707,22 +6707,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1879921919827012</v>
+        <v>0.1878532488091033</v>
       </c>
       <c r="C62">
-        <v>65.32437190530712</v>
+        <v>64.22107119619255</v>
       </c>
       <c r="D62">
-        <v>137.7143719053071</v>
+        <v>137.8490711961926</v>
       </c>
       <c r="E62">
-        <v>49.98</v>
+        <v>51.218</v>
       </c>
       <c r="F62">
-        <v>74.28</v>
+        <v>75.518</v>
       </c>
       <c r="G62">
         <v>1.89</v>
@@ -6743,28 +6743,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M62">
-        <v>4.761348000000001</v>
+        <v>4.8407038</v>
       </c>
       <c r="N62">
-        <v>10.8621213877551</v>
+        <v>10.7827655877551</v>
       </c>
       <c r="O62">
-        <v>1.629318208163265</v>
+        <v>1.617414838163265</v>
       </c>
       <c r="P62">
-        <v>9.232803179591833</v>
+        <v>9.165350749591836</v>
       </c>
       <c r="Q62">
-        <v>12.28280317959183</v>
+        <v>12.21535074959183</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3882529799567529</v>
+        <v>0.3964548687412906</v>
       </c>
       <c r="T62">
-        <v>2.094399795251704</v>
+        <v>2.144561526048097</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.28131222245362</v>
+        <v>3.22752021880684</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6789,22 +6789,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1878532488091033</v>
+        <v>0.1877143056355055</v>
       </c>
       <c r="C63">
-        <v>64.22107119619255</v>
+        <v>63.11803424550422</v>
       </c>
       <c r="D63">
-        <v>137.8490711961926</v>
+        <v>137.9840342455042</v>
       </c>
       <c r="E63">
-        <v>51.218</v>
+        <v>52.456</v>
       </c>
       <c r="F63">
-        <v>75.518</v>
+        <v>76.756</v>
       </c>
       <c r="G63">
         <v>1.89</v>
@@ -6825,28 +6825,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M63">
-        <v>4.8407038</v>
+        <v>4.9200596</v>
       </c>
       <c r="N63">
-        <v>10.7827655877551</v>
+        <v>10.7034097877551</v>
       </c>
       <c r="O63">
-        <v>1.617414838163265</v>
+        <v>1.605511468163265</v>
       </c>
       <c r="P63">
-        <v>9.165350749591836</v>
+        <v>9.097898319591836</v>
       </c>
       <c r="Q63">
-        <v>12.21535074959183</v>
+        <v>12.14789831959184</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3964548687412906</v>
+        <v>0.4050884358829092</v>
       </c>
       <c r="T63">
-        <v>2.144561526048097</v>
+        <v>2.197363347939036</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.22752021880684</v>
+        <v>3.175463441084149</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6871,22 +6871,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1877143056355055</v>
+        <v>0.1875753624619076</v>
       </c>
       <c r="C64">
-        <v>63.11803424550422</v>
+        <v>62.01526182871038</v>
       </c>
       <c r="D64">
-        <v>137.9840342455042</v>
+        <v>138.1192618287104</v>
       </c>
       <c r="E64">
-        <v>52.456</v>
+        <v>53.694</v>
       </c>
       <c r="F64">
-        <v>76.756</v>
+        <v>77.994</v>
       </c>
       <c r="G64">
         <v>1.89</v>
@@ -6907,28 +6907,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M64">
-        <v>4.9200596</v>
+        <v>4.9994154</v>
       </c>
       <c r="N64">
-        <v>10.7034097877551</v>
+        <v>10.6240539877551</v>
       </c>
       <c r="O64">
-        <v>1.605511468163265</v>
+        <v>1.593608098163265</v>
       </c>
       <c r="P64">
-        <v>9.097898319591836</v>
+        <v>9.030445889591835</v>
       </c>
       <c r="Q64">
-        <v>12.14789831959184</v>
+        <v>12.08044588959184</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4050884358829092</v>
+        <v>0.4141886823294801</v>
       </c>
       <c r="T64">
-        <v>2.197363347939036</v>
+        <v>2.25301932236462</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.175463441084149</v>
+        <v>3.125059259479638</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6953,22 +6953,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1875753624619076</v>
+        <v>0.1874364192883098</v>
       </c>
       <c r="C65">
-        <v>62.01526182871038</v>
+        <v>60.91275472432233</v>
       </c>
       <c r="D65">
-        <v>138.1192618287104</v>
+        <v>138.2547547243223</v>
       </c>
       <c r="E65">
-        <v>53.694</v>
+        <v>54.932</v>
       </c>
       <c r="F65">
-        <v>77.994</v>
+        <v>79.232</v>
       </c>
       <c r="G65">
         <v>1.89</v>
@@ -6989,28 +6989,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M65">
-        <v>4.9994154</v>
+        <v>5.0787712</v>
       </c>
       <c r="N65">
-        <v>10.6240539877551</v>
+        <v>10.5446981877551</v>
       </c>
       <c r="O65">
-        <v>1.593608098163265</v>
+        <v>1.581704728163265</v>
       </c>
       <c r="P65">
-        <v>9.030445889591835</v>
+        <v>8.962993459591836</v>
       </c>
       <c r="Q65">
-        <v>12.08044588959184</v>
+        <v>12.01299345959184</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4141886823294801</v>
+        <v>0.4237944980230827</v>
       </c>
       <c r="T65">
-        <v>2.25301932236462</v>
+        <v>2.311767295369403</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.125059259479638</v>
+        <v>3.076230208550269</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7035,22 +7035,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1874364192883098</v>
+        <v>0.1872974761147119</v>
       </c>
       <c r="C66">
-        <v>60.91275472432233</v>
+        <v>59.81051371390893</v>
       </c>
       <c r="D66">
-        <v>138.2547547243223</v>
+        <v>138.3905137139089</v>
       </c>
       <c r="E66">
-        <v>54.932</v>
+        <v>56.17</v>
       </c>
       <c r="F66">
-        <v>79.232</v>
+        <v>80.47</v>
       </c>
       <c r="G66">
         <v>1.89</v>
@@ -7071,28 +7071,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M66">
-        <v>5.0787712</v>
+        <v>5.158127</v>
       </c>
       <c r="N66">
-        <v>10.5446981877551</v>
+        <v>10.4653423877551</v>
       </c>
       <c r="O66">
-        <v>1.581704728163265</v>
+        <v>1.569801358163265</v>
       </c>
       <c r="P66">
-        <v>8.962993459591836</v>
+        <v>8.895541029591836</v>
       </c>
       <c r="Q66">
-        <v>12.01299345959184</v>
+        <v>11.94554102959184</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4237944980230827</v>
+        <v>0.4339492174706054</v>
       </c>
       <c r="T66">
-        <v>2.311767295369403</v>
+        <v>2.373872295403031</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.076230208550269</v>
+        <v>3.028903589957188</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7117,22 +7117,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1872974761147119</v>
+        <v>0.191534332941114</v>
       </c>
       <c r="C67">
-        <v>59.81051371390893</v>
+        <v>54.5491598417984</v>
       </c>
       <c r="D67">
-        <v>138.3905137139089</v>
+        <v>134.3671598417984</v>
       </c>
       <c r="E67">
-        <v>56.17</v>
+        <v>57.408</v>
       </c>
       <c r="F67">
-        <v>80.47</v>
+        <v>81.708</v>
       </c>
       <c r="G67">
         <v>1.89</v>
@@ -7153,45 +7153,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M67">
-        <v>5.158127</v>
+        <v>5.8748052</v>
       </c>
       <c r="N67">
-        <v>10.4653423877551</v>
+        <v>9.7486641877551</v>
       </c>
       <c r="O67">
-        <v>1.569801358163265</v>
+        <v>1.462299628163265</v>
       </c>
       <c r="P67">
-        <v>8.895541029591836</v>
+        <v>8.286364559591835</v>
       </c>
       <c r="Q67">
-        <v>11.94554102959184</v>
+        <v>11.33636455959184</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4339492174706054</v>
+        <v>0.4447012733562178</v>
       </c>
       <c r="T67">
-        <v>2.373872295403031</v>
+        <v>2.439630530732755</v>
       </c>
       <c r="U67">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V67">
         <v>0.15</v>
       </c>
       <c r="W67">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.028903589957188</v>
+        <v>2.659402117325541</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7199,22 +7199,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.191534332941114</v>
+        <v>0.1914616897675162</v>
       </c>
       <c r="C68">
-        <v>54.5491598417984</v>
+        <v>53.37817030236508</v>
       </c>
       <c r="D68">
-        <v>134.3671598417984</v>
+        <v>134.4341703023651</v>
       </c>
       <c r="E68">
-        <v>57.408</v>
+        <v>58.646</v>
       </c>
       <c r="F68">
-        <v>81.708</v>
+        <v>82.946</v>
       </c>
       <c r="G68">
         <v>1.89</v>
@@ -7235,28 +7235,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M68">
-        <v>5.8748052</v>
+        <v>5.9638174</v>
       </c>
       <c r="N68">
-        <v>9.7486641877551</v>
+        <v>9.659651987755101</v>
       </c>
       <c r="O68">
-        <v>1.462299628163265</v>
+        <v>1.448947798163265</v>
       </c>
       <c r="P68">
-        <v>8.286364559591835</v>
+        <v>8.210704189591835</v>
       </c>
       <c r="Q68">
-        <v>11.33636455959184</v>
+        <v>11.26070418959183</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4447012733562178</v>
+        <v>0.4561049689924733</v>
       </c>
       <c r="T68">
-        <v>2.439630530732755</v>
+        <v>2.50937411365822</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.659402117325541</v>
+        <v>2.619709548410235</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7281,22 +7281,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1914616897675162</v>
+        <v>0.1913890465939183</v>
       </c>
       <c r="C69">
-        <v>53.37817030236508</v>
+        <v>52.20724763406847</v>
       </c>
       <c r="D69">
-        <v>134.4341703023651</v>
+        <v>134.5012476340685</v>
       </c>
       <c r="E69">
-        <v>58.646</v>
+        <v>59.884</v>
       </c>
       <c r="F69">
-        <v>82.946</v>
+        <v>84.184</v>
       </c>
       <c r="G69">
         <v>1.89</v>
@@ -7317,28 +7317,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M69">
-        <v>5.9638174</v>
+        <v>6.0528296</v>
       </c>
       <c r="N69">
-        <v>9.659651987755101</v>
+        <v>9.570639787755102</v>
       </c>
       <c r="O69">
-        <v>1.448947798163265</v>
+        <v>1.435595968163265</v>
       </c>
       <c r="P69">
-        <v>8.210704189591835</v>
+        <v>8.135043819591836</v>
       </c>
       <c r="Q69">
-        <v>11.26070418959183</v>
+        <v>11.18504381959184</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4561049689924733</v>
+        <v>0.4682213956059949</v>
       </c>
       <c r="T69">
-        <v>2.50937411365822</v>
+        <v>2.583476670516526</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.619709548410235</v>
+        <v>2.581184407992438</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7363,22 +7363,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1913890465939183</v>
+        <v>0.1913164034203205</v>
       </c>
       <c r="C70">
-        <v>52.20724763406847</v>
+        <v>51.03639193705668</v>
       </c>
       <c r="D70">
-        <v>134.5012476340685</v>
+        <v>134.5683919370567</v>
       </c>
       <c r="E70">
-        <v>59.884</v>
+        <v>61.12200000000001</v>
       </c>
       <c r="F70">
-        <v>84.184</v>
+        <v>85.42200000000001</v>
       </c>
       <c r="G70">
         <v>1.89</v>
@@ -7399,28 +7399,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M70">
-        <v>6.0528296</v>
+        <v>6.141841800000002</v>
       </c>
       <c r="N70">
-        <v>9.570639787755102</v>
+        <v>9.481627587755099</v>
       </c>
       <c r="O70">
-        <v>1.435595968163265</v>
+        <v>1.422244138163265</v>
       </c>
       <c r="P70">
-        <v>8.135043819591836</v>
+        <v>8.059383449591834</v>
       </c>
       <c r="Q70">
-        <v>11.18504381959184</v>
+        <v>11.10938344959184</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4682213956059949</v>
+        <v>0.4811195271623241</v>
       </c>
       <c r="T70">
-        <v>2.583476670516526</v>
+        <v>2.662360037494723</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.581184407992438</v>
+        <v>2.543775938311387</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7445,22 +7445,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1913164034203205</v>
+        <v>0.1912437602467226</v>
       </c>
       <c r="C71">
-        <v>51.03639193705668</v>
+        <v>49.86560331167793</v>
       </c>
       <c r="D71">
-        <v>134.5683919370567</v>
+        <v>134.635603311678</v>
       </c>
       <c r="E71">
-        <v>61.12200000000001</v>
+        <v>62.36000000000001</v>
       </c>
       <c r="F71">
-        <v>85.42200000000001</v>
+        <v>86.66000000000001</v>
       </c>
       <c r="G71">
         <v>1.89</v>
@@ -7481,28 +7481,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M71">
-        <v>6.141841800000002</v>
+        <v>6.230854000000002</v>
       </c>
       <c r="N71">
-        <v>9.481627587755099</v>
+        <v>9.3926153877551</v>
       </c>
       <c r="O71">
-        <v>1.422244138163265</v>
+        <v>1.408892308163265</v>
       </c>
       <c r="P71">
-        <v>8.059383449591834</v>
+        <v>7.983723079591835</v>
       </c>
       <c r="Q71">
-        <v>11.10938344959184</v>
+        <v>11.03372307959183</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4811195271623241</v>
+        <v>0.4948775341557421</v>
       </c>
       <c r="T71">
-        <v>2.662360037494723</v>
+        <v>2.7465022956048</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.543775938311387</v>
+        <v>2.507436282049796</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7527,22 +7527,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1912437602467226</v>
+        <v>0.1935247670731248</v>
       </c>
       <c r="C72">
-        <v>49.86560331167793</v>
+        <v>46.54870526150405</v>
       </c>
       <c r="D72">
-        <v>134.635603311678</v>
+        <v>132.5567052615041</v>
       </c>
       <c r="E72">
-        <v>62.36000000000001</v>
+        <v>63.59800000000001</v>
       </c>
       <c r="F72">
-        <v>86.66000000000001</v>
+        <v>87.89800000000001</v>
       </c>
       <c r="G72">
         <v>1.89</v>
@@ -7563,45 +7563,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M72">
-        <v>6.230854000000002</v>
+        <v>6.662668400000001</v>
       </c>
       <c r="N72">
-        <v>9.3926153877551</v>
+        <v>8.9608009877551</v>
       </c>
       <c r="O72">
-        <v>1.408892308163265</v>
+        <v>1.344120148163265</v>
       </c>
       <c r="P72">
-        <v>7.983723079591835</v>
+        <v>7.616680839591835</v>
       </c>
       <c r="Q72">
-        <v>11.03372307959183</v>
+        <v>10.66668083959183</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4948775341557421</v>
+        <v>0.5095843692176717</v>
       </c>
       <c r="T72">
-        <v>2.7465022956048</v>
+        <v>2.836447468067297</v>
       </c>
       <c r="U72">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V72">
         <v>0.15</v>
       </c>
       <c r="W72">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.507436282049796</v>
+        <v>2.34492675453503</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7609,22 +7609,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1935247670731247</v>
+        <v>0.1934852738995269</v>
       </c>
       <c r="C73">
-        <v>46.5487052615041</v>
+        <v>45.34615283751637</v>
       </c>
       <c r="D73">
-        <v>132.5567052615041</v>
+        <v>132.5921528375164</v>
       </c>
       <c r="E73">
-        <v>63.598</v>
+        <v>64.836</v>
       </c>
       <c r="F73">
-        <v>87.898</v>
+        <v>89.136</v>
       </c>
       <c r="G73">
         <v>1.89</v>
@@ -7645,28 +7645,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M73">
-        <v>6.6626684</v>
+        <v>6.756508800000001</v>
       </c>
       <c r="N73">
-        <v>8.9608009877551</v>
+        <v>8.8669605877551</v>
       </c>
       <c r="O73">
-        <v>1.344120148163265</v>
+        <v>1.330044088163265</v>
       </c>
       <c r="P73">
-        <v>7.616680839591835</v>
+        <v>7.536916499591835</v>
       </c>
       <c r="Q73">
-        <v>10.66668083959183</v>
+        <v>10.58691649959184</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5095843692176715</v>
+        <v>0.5253416924983103</v>
       </c>
       <c r="T73">
-        <v>2.836447468067295</v>
+        <v>2.932817295705684</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.34492675453503</v>
+        <v>2.31235832738871</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7691,22 +7691,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1934852738995269</v>
+        <v>0.193445780725929</v>
       </c>
       <c r="C74">
-        <v>45.34615283751637</v>
+        <v>44.14361937698663</v>
       </c>
       <c r="D74">
-        <v>132.5921528375164</v>
+        <v>132.6276193769866</v>
       </c>
       <c r="E74">
-        <v>64.836</v>
+        <v>66.074</v>
       </c>
       <c r="F74">
-        <v>89.136</v>
+        <v>90.374</v>
       </c>
       <c r="G74">
         <v>1.89</v>
@@ -7727,28 +7727,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M74">
-        <v>6.756508800000001</v>
+        <v>6.8503492</v>
       </c>
       <c r="N74">
-        <v>8.8669605877551</v>
+        <v>8.773120187755101</v>
       </c>
       <c r="O74">
-        <v>1.330044088163265</v>
+        <v>1.315968028163265</v>
       </c>
       <c r="P74">
-        <v>7.536916499591835</v>
+        <v>7.457152159591836</v>
       </c>
       <c r="Q74">
-        <v>10.58691649959184</v>
+        <v>10.50715215959184</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5253416924983103</v>
+        <v>0.5422662249108482</v>
       </c>
       <c r="T74">
-        <v>2.932817295705684</v>
+        <v>3.036325629095064</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.31235832738871</v>
+        <v>2.280682185917632</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7773,22 +7773,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.193445780725929</v>
+        <v>0.1934062875523312</v>
       </c>
       <c r="C75">
-        <v>44.14361937698663</v>
+        <v>42.94110489513616</v>
       </c>
       <c r="D75">
-        <v>132.6276193769866</v>
+        <v>132.6631048951362</v>
       </c>
       <c r="E75">
-        <v>66.074</v>
+        <v>67.312</v>
       </c>
       <c r="F75">
-        <v>90.374</v>
+        <v>91.61199999999999</v>
       </c>
       <c r="G75">
         <v>1.89</v>
@@ -7809,28 +7809,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M75">
-        <v>6.8503492</v>
+        <v>6.944189600000001</v>
       </c>
       <c r="N75">
-        <v>8.773120187755101</v>
+        <v>8.6792797877551</v>
       </c>
       <c r="O75">
-        <v>1.315968028163265</v>
+        <v>1.301891968163265</v>
       </c>
       <c r="P75">
-        <v>7.457152159591836</v>
+        <v>7.377387819591835</v>
       </c>
       <c r="Q75">
-        <v>10.50715215959184</v>
+        <v>10.42738781959184</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5422662249108482</v>
+        <v>0.5604926444320429</v>
       </c>
       <c r="T75">
-        <v>3.036325629095064</v>
+        <v>3.147796141975935</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.280682185917632</v>
+        <v>2.249862156378204</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7855,22 +7855,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1934062875523312</v>
+        <v>0.1933667943787333</v>
       </c>
       <c r="C76">
-        <v>42.94110489513616</v>
+        <v>41.73860940720277</v>
       </c>
       <c r="D76">
-        <v>132.6631048951362</v>
+        <v>132.6986094072028</v>
       </c>
       <c r="E76">
-        <v>67.312</v>
+        <v>68.55</v>
       </c>
       <c r="F76">
-        <v>91.61199999999999</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="G76">
         <v>1.89</v>
@@ -7891,28 +7891,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M76">
-        <v>6.944189600000001</v>
+        <v>7.03803</v>
       </c>
       <c r="N76">
-        <v>8.6792797877551</v>
+        <v>8.585439387755102</v>
       </c>
       <c r="O76">
-        <v>1.301891968163265</v>
+        <v>1.287815908163265</v>
       </c>
       <c r="P76">
-        <v>7.377387819591835</v>
+        <v>7.297623479591836</v>
       </c>
       <c r="Q76">
-        <v>10.42738781959184</v>
+        <v>10.34762347959184</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5604926444320429</v>
+        <v>0.5801771775149333</v>
       </c>
       <c r="T76">
-        <v>3.147796141975935</v>
+        <v>3.268184295887276</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.249862156378204</v>
+        <v>2.219863994293162</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7937,22 +7937,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1933667943787333</v>
+        <v>0.1933273012051354</v>
       </c>
       <c r="C77">
-        <v>41.73860940720277</v>
+        <v>40.53613292844059</v>
       </c>
       <c r="D77">
-        <v>132.6986094072028</v>
+        <v>132.7341329284406</v>
       </c>
       <c r="E77">
-        <v>68.55</v>
+        <v>69.788</v>
       </c>
       <c r="F77">
-        <v>92.84999999999999</v>
+        <v>94.08799999999999</v>
       </c>
       <c r="G77">
         <v>1.89</v>
@@ -7973,28 +7973,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M77">
-        <v>7.03803</v>
+        <v>7.1318704</v>
       </c>
       <c r="N77">
-        <v>8.585439387755102</v>
+        <v>8.491598987755101</v>
       </c>
       <c r="O77">
-        <v>1.287815908163265</v>
+        <v>1.273739848163265</v>
       </c>
       <c r="P77">
-        <v>7.297623479591836</v>
+        <v>7.217859139591836</v>
       </c>
       <c r="Q77">
-        <v>10.34762347959184</v>
+        <v>10.26785913959183</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5801771775149333</v>
+        <v>0.6015020883547311</v>
       </c>
       <c r="T77">
-        <v>3.268184295887276</v>
+        <v>3.398604795957895</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.219863994293162</v>
+        <v>2.190655257526146</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8019,22 +8019,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1933273012051354</v>
+        <v>0.1932878080315376</v>
       </c>
       <c r="C78">
-        <v>40.53613292844059</v>
+        <v>39.33367547411993</v>
       </c>
       <c r="D78">
-        <v>132.7341329284406</v>
+        <v>132.7696754741199</v>
       </c>
       <c r="E78">
-        <v>69.788</v>
+        <v>71.026</v>
       </c>
       <c r="F78">
-        <v>94.08799999999999</v>
+        <v>95.32599999999999</v>
       </c>
       <c r="G78">
         <v>1.89</v>
@@ -8055,28 +8055,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M78">
-        <v>7.1318704</v>
+        <v>7.2257108</v>
       </c>
       <c r="N78">
-        <v>8.491598987755101</v>
+        <v>8.397758587755101</v>
       </c>
       <c r="O78">
-        <v>1.273739848163265</v>
+        <v>1.259663788163265</v>
       </c>
       <c r="P78">
-        <v>7.217859139591836</v>
+        <v>7.138094799591836</v>
       </c>
       <c r="Q78">
-        <v>10.26785913959183</v>
+        <v>10.18809479959184</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6015020883547311</v>
+        <v>0.6246813392675546</v>
       </c>
       <c r="T78">
-        <v>3.398604795957895</v>
+        <v>3.540366209078133</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.190655257526146</v>
+        <v>2.162205189246586</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8101,22 +8101,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1932878080315376</v>
+        <v>0.1932483148579397</v>
       </c>
       <c r="C79">
-        <v>39.33367547411993</v>
+        <v>38.13123705952752</v>
       </c>
       <c r="D79">
-        <v>132.7696754741199</v>
+        <v>132.8052370595275</v>
       </c>
       <c r="E79">
-        <v>71.026</v>
+        <v>72.26400000000001</v>
       </c>
       <c r="F79">
-        <v>95.32599999999999</v>
+        <v>96.56400000000001</v>
       </c>
       <c r="G79">
         <v>1.89</v>
@@ -8137,28 +8137,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M79">
-        <v>7.2257108</v>
+        <v>7.319551200000001</v>
       </c>
       <c r="N79">
-        <v>8.397758587755101</v>
+        <v>8.3039181877551</v>
       </c>
       <c r="O79">
-        <v>1.259663788163265</v>
+        <v>1.245587728163265</v>
       </c>
       <c r="P79">
-        <v>7.138094799591836</v>
+        <v>7.058330459591835</v>
       </c>
       <c r="Q79">
-        <v>10.18809479959184</v>
+        <v>10.10833045959183</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6246813392675546</v>
+        <v>0.6499677948088169</v>
       </c>
       <c r="T79">
-        <v>3.540366209078133</v>
+        <v>3.69501502339112</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.162205189246586</v>
+        <v>2.134484609897271</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8183,22 +8183,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1932483148579397</v>
+        <v>0.1932088216843418</v>
       </c>
       <c r="C80">
-        <v>38.13123705952752</v>
+        <v>36.92881769996661</v>
       </c>
       <c r="D80">
-        <v>132.8052370595275</v>
+        <v>132.8408176999666</v>
       </c>
       <c r="E80">
-        <v>72.26400000000001</v>
+        <v>73.50200000000001</v>
       </c>
       <c r="F80">
-        <v>96.56400000000001</v>
+        <v>97.80200000000001</v>
       </c>
       <c r="G80">
         <v>1.89</v>
@@ -8219,28 +8219,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M80">
-        <v>7.319551200000001</v>
+        <v>7.413391600000002</v>
       </c>
       <c r="N80">
-        <v>8.3039181877551</v>
+        <v>8.2100777877551</v>
       </c>
       <c r="O80">
-        <v>1.245587728163265</v>
+        <v>1.231511668163265</v>
       </c>
       <c r="P80">
-        <v>7.058330459591835</v>
+        <v>6.978566119591836</v>
       </c>
       <c r="Q80">
-        <v>10.10833045959183</v>
+        <v>10.02856611959184</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6499677948088169</v>
+        <v>0.6776624842111517</v>
       </c>
       <c r="T80">
-        <v>3.69501502339112</v>
+        <v>3.864392296210105</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.134484609897271</v>
+        <v>2.107465817366926</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8265,22 +8265,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1932088216843418</v>
+        <v>0.193169328510744</v>
       </c>
       <c r="C81">
-        <v>36.92881769996661</v>
+        <v>35.72641741075667</v>
       </c>
       <c r="D81">
-        <v>132.8408176999666</v>
+        <v>132.8764174107567</v>
       </c>
       <c r="E81">
-        <v>73.50200000000001</v>
+        <v>74.74000000000001</v>
       </c>
       <c r="F81">
-        <v>97.80200000000001</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="G81">
         <v>1.89</v>
@@ -8301,28 +8301,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M81">
-        <v>7.413391600000002</v>
+        <v>7.507232000000001</v>
       </c>
       <c r="N81">
-        <v>8.2100777877551</v>
+        <v>8.116237387755099</v>
       </c>
       <c r="O81">
-        <v>1.231511668163265</v>
+        <v>1.217435608163265</v>
       </c>
       <c r="P81">
-        <v>6.978566119591836</v>
+        <v>6.898801779591834</v>
       </c>
       <c r="Q81">
-        <v>10.02856611959184</v>
+        <v>9.948801779591834</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6776624842111517</v>
+        <v>0.70812664255372</v>
       </c>
       <c r="T81">
-        <v>3.864392296210105</v>
+        <v>4.05070729631099</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.107465817366926</v>
+        <v>2.081122494649839</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8347,22 +8347,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.193169328510744</v>
+        <v>0.1931298353371462</v>
       </c>
       <c r="C82">
-        <v>35.72641741075667</v>
+        <v>34.52403620723361</v>
       </c>
       <c r="D82">
-        <v>132.8764174107567</v>
+        <v>132.9120362072336</v>
       </c>
       <c r="E82">
-        <v>74.74000000000001</v>
+        <v>75.97800000000001</v>
       </c>
       <c r="F82">
-        <v>99.04000000000001</v>
+        <v>100.278</v>
       </c>
       <c r="G82">
         <v>1.89</v>
@@ -8383,28 +8383,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M82">
-        <v>7.507232000000001</v>
+        <v>7.601072400000001</v>
       </c>
       <c r="N82">
-        <v>8.116237387755099</v>
+        <v>8.0223969877551</v>
       </c>
       <c r="O82">
-        <v>1.217435608163265</v>
+        <v>1.203359548163265</v>
       </c>
       <c r="P82">
-        <v>6.898801779591834</v>
+        <v>6.819037439591835</v>
       </c>
       <c r="Q82">
-        <v>9.948801779591834</v>
+        <v>9.869037439591835</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.70812664255372</v>
+        <v>0.7417975544060326</v>
       </c>
       <c r="T82">
-        <v>4.05070729631099</v>
+        <v>4.256634401685653</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.081122494649839</v>
+        <v>2.055429624345519</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8429,22 +8429,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1931298353371462</v>
+        <v>0.1930903421635483</v>
       </c>
       <c r="C83">
-        <v>34.52403620723361</v>
+        <v>33.32167410475004</v>
       </c>
       <c r="D83">
-        <v>132.9120362072336</v>
+        <v>132.9476741047501</v>
       </c>
       <c r="E83">
-        <v>75.97800000000001</v>
+        <v>77.21600000000001</v>
       </c>
       <c r="F83">
-        <v>100.278</v>
+        <v>101.516</v>
       </c>
       <c r="G83">
         <v>1.89</v>
@@ -8465,28 +8465,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M83">
-        <v>7.601072400000001</v>
+        <v>7.694912800000001</v>
       </c>
       <c r="N83">
-        <v>8.0223969877551</v>
+        <v>7.9285565877551</v>
       </c>
       <c r="O83">
-        <v>1.203359548163265</v>
+        <v>1.189283488163265</v>
       </c>
       <c r="P83">
-        <v>6.819037439591835</v>
+        <v>6.739273099591835</v>
       </c>
       <c r="Q83">
-        <v>9.869037439591835</v>
+        <v>9.789273099591835</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7417975544060326</v>
+        <v>0.7792096786863796</v>
       </c>
       <c r="T83">
-        <v>4.256634401685653</v>
+        <v>4.485442296546387</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.055429624345519</v>
+        <v>2.030363409414477</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8511,22 +8511,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1930903421635483</v>
+        <v>0.1930508489899505</v>
       </c>
       <c r="C84">
-        <v>33.32167410475004</v>
+        <v>32.11933111867465</v>
       </c>
       <c r="D84">
-        <v>132.9476741047501</v>
+        <v>132.9833311186747</v>
       </c>
       <c r="E84">
-        <v>77.21600000000001</v>
+        <v>78.45400000000001</v>
       </c>
       <c r="F84">
-        <v>101.516</v>
+        <v>102.754</v>
       </c>
       <c r="G84">
         <v>1.89</v>
@@ -8547,28 +8547,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M84">
-        <v>7.694912800000001</v>
+        <v>7.788753200000001</v>
       </c>
       <c r="N84">
-        <v>7.9285565877551</v>
+        <v>7.8347161877551</v>
       </c>
       <c r="O84">
-        <v>1.189283488163265</v>
+        <v>1.175207428163265</v>
       </c>
       <c r="P84">
-        <v>6.739273099591835</v>
+        <v>6.659508759591835</v>
       </c>
       <c r="Q84">
-        <v>9.789273099591835</v>
+        <v>9.709508759591834</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7792096786863796</v>
+        <v>0.8210232293526499</v>
       </c>
       <c r="T84">
-        <v>4.485442296546387</v>
+        <v>4.741168767273092</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.030363409414477</v>
+        <v>2.005901199662495</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8593,22 +8593,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1930508489899505</v>
+        <v>0.2031501558163526</v>
       </c>
       <c r="C85">
-        <v>32.11933111867465</v>
+        <v>22.34597596254744</v>
       </c>
       <c r="D85">
-        <v>132.9833311186747</v>
+        <v>124.4479759625474</v>
       </c>
       <c r="E85">
-        <v>78.45400000000001</v>
+        <v>79.69200000000001</v>
       </c>
       <c r="F85">
-        <v>102.754</v>
+        <v>103.992</v>
       </c>
       <c r="G85">
         <v>1.89</v>
@@ -8629,45 +8629,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M85">
-        <v>7.788753200000001</v>
+        <v>9.35928</v>
       </c>
       <c r="N85">
-        <v>7.8347161877551</v>
+        <v>6.264189387755101</v>
       </c>
       <c r="O85">
-        <v>1.175207428163265</v>
+        <v>0.9396284081632651</v>
       </c>
       <c r="P85">
-        <v>6.659508759591835</v>
+        <v>5.324560979591836</v>
       </c>
       <c r="Q85">
-        <v>9.709508759591834</v>
+        <v>8.374560979591836</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.8210232293526499</v>
+        <v>0.8680634738522039</v>
       </c>
       <c r="T85">
-        <v>4.741168767273092</v>
+        <v>5.028861046840635</v>
       </c>
       <c r="U85">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V85">
         <v>0.15</v>
       </c>
       <c r="W85">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y85">
-        <v>2.005901199662495</v>
+        <v>1.66930248777204</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8675,22 +8675,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2031501558163526</v>
+        <v>0.2032313626427547</v>
       </c>
       <c r="C86">
-        <v>22.34597596254746</v>
+        <v>21.04378274837181</v>
       </c>
       <c r="D86">
-        <v>124.4479759625474</v>
+        <v>124.3837827483718</v>
       </c>
       <c r="E86">
-        <v>79.69199999999999</v>
+        <v>80.92999999999999</v>
       </c>
       <c r="F86">
-        <v>103.992</v>
+        <v>105.23</v>
       </c>
       <c r="G86">
         <v>1.89</v>
@@ -8711,28 +8711,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M86">
-        <v>9.359279999999998</v>
+        <v>9.470699999999999</v>
       </c>
       <c r="N86">
-        <v>6.264189387755103</v>
+        <v>6.152769387755102</v>
       </c>
       <c r="O86">
-        <v>0.9396284081632653</v>
+        <v>0.9229154081632652</v>
       </c>
       <c r="P86">
-        <v>5.324560979591837</v>
+        <v>5.229853979591836</v>
       </c>
       <c r="Q86">
-        <v>8.374560979591838</v>
+        <v>8.279853979591836</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8680634738522035</v>
+        <v>0.9213757509516981</v>
       </c>
       <c r="T86">
-        <v>5.028861046840632</v>
+        <v>5.354912297017179</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.669302487772041</v>
+        <v>1.649663634974722</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8757,22 +8757,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2032313626427547</v>
+        <v>0.2033125694691568</v>
       </c>
       <c r="C87">
-        <v>21.04378274837181</v>
+        <v>19.74165572481476</v>
       </c>
       <c r="D87">
-        <v>124.3837827483718</v>
+        <v>124.3196557248148</v>
       </c>
       <c r="E87">
-        <v>80.92999999999999</v>
+        <v>82.16799999999999</v>
       </c>
       <c r="F87">
-        <v>105.23</v>
+        <v>106.468</v>
       </c>
       <c r="G87">
         <v>1.89</v>
@@ -8793,28 +8793,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M87">
-        <v>9.470699999999999</v>
+        <v>9.582119999999998</v>
       </c>
       <c r="N87">
-        <v>6.152769387755102</v>
+        <v>6.041349387755103</v>
       </c>
       <c r="O87">
-        <v>0.9229154081632652</v>
+        <v>0.9062024081632654</v>
       </c>
       <c r="P87">
-        <v>5.229853979591836</v>
+        <v>5.135146979591838</v>
       </c>
       <c r="Q87">
-        <v>8.279853979591836</v>
+        <v>8.185146979591838</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.9213757509516981</v>
+        <v>0.9823040676368345</v>
       </c>
       <c r="T87">
-        <v>5.354912297017179</v>
+        <v>5.727542297218947</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.649663634974722</v>
+        <v>1.630481499684319</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8839,22 +8839,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2033125694691568</v>
+        <v>0.203393776295559</v>
       </c>
       <c r="C88">
-        <v>19.74165572481476</v>
+        <v>18.43959478955364</v>
       </c>
       <c r="D88">
-        <v>124.3196557248148</v>
+        <v>124.2555947895536</v>
       </c>
       <c r="E88">
-        <v>82.16799999999999</v>
+        <v>83.40600000000001</v>
       </c>
       <c r="F88">
-        <v>106.468</v>
+        <v>107.706</v>
       </c>
       <c r="G88">
         <v>1.89</v>
@@ -8875,28 +8875,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M88">
-        <v>9.582119999999998</v>
+        <v>9.69354</v>
       </c>
       <c r="N88">
-        <v>6.041349387755103</v>
+        <v>5.9299293877551</v>
       </c>
       <c r="O88">
-        <v>0.9062024081632654</v>
+        <v>0.889489408163265</v>
       </c>
       <c r="P88">
-        <v>5.135146979591838</v>
+        <v>5.040439979591835</v>
       </c>
       <c r="Q88">
-        <v>8.185146979591838</v>
+        <v>8.090439979591835</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9823040676368345</v>
+        <v>1.0526059715043</v>
       </c>
       <c r="T88">
-        <v>5.727542297218947</v>
+        <v>6.157499989759449</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.630481499684319</v>
+        <v>1.61174033302128</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8921,22 +8921,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.203393776295559</v>
+        <v>0.2034749831219612</v>
       </c>
       <c r="C89">
-        <v>18.43959478955364</v>
+        <v>17.13759984047685</v>
       </c>
       <c r="D89">
-        <v>124.2555947895536</v>
+        <v>124.1915998404769</v>
       </c>
       <c r="E89">
-        <v>83.40600000000001</v>
+        <v>84.64400000000001</v>
       </c>
       <c r="F89">
-        <v>107.706</v>
+        <v>108.944</v>
       </c>
       <c r="G89">
         <v>1.89</v>
@@ -8957,28 +8957,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M89">
-        <v>9.69354</v>
+        <v>9.804959999999999</v>
       </c>
       <c r="N89">
-        <v>5.9299293877551</v>
+        <v>5.818509387755102</v>
       </c>
       <c r="O89">
-        <v>0.889489408163265</v>
+        <v>0.8727764081632652</v>
       </c>
       <c r="P89">
-        <v>5.040439979591835</v>
+        <v>4.945732979591837</v>
       </c>
       <c r="Q89">
-        <v>8.090439979591835</v>
+        <v>7.995732979591836</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.0526059715043</v>
+        <v>1.134624859349676</v>
       </c>
       <c r="T89">
-        <v>6.157499989759449</v>
+        <v>6.65911729772337</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.61174033302128</v>
+        <v>1.59342510196422</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9003,22 +9003,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2034749831219612</v>
+        <v>0.2035561899483633</v>
       </c>
       <c r="C90">
-        <v>17.13759984047685</v>
+        <v>15.83567077568297</v>
       </c>
       <c r="D90">
-        <v>124.1915998404769</v>
+        <v>124.127670775683</v>
       </c>
       <c r="E90">
-        <v>84.64400000000001</v>
+        <v>85.88200000000001</v>
       </c>
       <c r="F90">
-        <v>108.944</v>
+        <v>110.182</v>
       </c>
       <c r="G90">
         <v>1.89</v>
@@ -9039,28 +9039,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M90">
-        <v>9.804959999999999</v>
+        <v>9.91638</v>
       </c>
       <c r="N90">
-        <v>5.818509387755102</v>
+        <v>5.707089387755101</v>
       </c>
       <c r="O90">
-        <v>0.8727764081632652</v>
+        <v>0.8560634081632651</v>
       </c>
       <c r="P90">
-        <v>4.945732979591837</v>
+        <v>4.851025979591836</v>
       </c>
       <c r="Q90">
-        <v>7.995732979591836</v>
+        <v>7.901025979591836</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.134624859349676</v>
+        <v>1.231556272257848</v>
       </c>
       <c r="T90">
-        <v>6.65911729772337</v>
+        <v>7.25193775258982</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.59342510196422</v>
+        <v>1.575521449133162</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9085,22 +9085,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2035561899483633</v>
+        <v>0.2036373967747654</v>
       </c>
       <c r="C91">
-        <v>15.83567077568297</v>
+        <v>14.53380749348015</v>
       </c>
       <c r="D91">
-        <v>124.127670775683</v>
+        <v>124.0638074934802</v>
       </c>
       <c r="E91">
-        <v>85.88200000000001</v>
+        <v>87.12</v>
       </c>
       <c r="F91">
-        <v>110.182</v>
+        <v>111.42</v>
       </c>
       <c r="G91">
         <v>1.89</v>
@@ -9121,28 +9121,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M91">
-        <v>9.91638</v>
+        <v>10.0278</v>
       </c>
       <c r="N91">
-        <v>5.707089387755101</v>
+        <v>5.595669387755102</v>
       </c>
       <c r="O91">
-        <v>0.8560634081632651</v>
+        <v>0.8393504081632652</v>
       </c>
       <c r="P91">
-        <v>4.851025979591836</v>
+        <v>4.756318979591836</v>
       </c>
       <c r="Q91">
-        <v>7.901025979591836</v>
+        <v>7.806318979591836</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.231556272257848</v>
+        <v>1.347873967747655</v>
       </c>
       <c r="T91">
-        <v>7.25193775258982</v>
+        <v>7.963322298429561</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.575521449133162</v>
+        <v>1.558015655253904</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9167,22 +9167,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2036373967747654</v>
+        <v>0.2037186036011676</v>
       </c>
       <c r="C92">
-        <v>14.53380749348015</v>
+        <v>13.23200989238589</v>
       </c>
       <c r="D92">
-        <v>124.0638074934802</v>
+        <v>124.0000098923859</v>
       </c>
       <c r="E92">
-        <v>87.12</v>
+        <v>88.358</v>
       </c>
       <c r="F92">
-        <v>111.42</v>
+        <v>112.658</v>
       </c>
       <c r="G92">
         <v>1.89</v>
@@ -9203,28 +9203,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M92">
-        <v>10.0278</v>
+        <v>10.13922</v>
       </c>
       <c r="N92">
-        <v>5.595669387755102</v>
+        <v>5.484249387755101</v>
       </c>
       <c r="O92">
-        <v>0.8393504081632652</v>
+        <v>0.8226374081632651</v>
       </c>
       <c r="P92">
-        <v>4.756318979591836</v>
+        <v>4.661611979591836</v>
       </c>
       <c r="Q92">
-        <v>7.806318979591836</v>
+        <v>7.711611979591836</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.347873967747655</v>
+        <v>1.490040040012973</v>
       </c>
       <c r="T92">
-        <v>7.963322298429561</v>
+        <v>8.832792298900355</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.558015655253904</v>
+        <v>1.540894604097268</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9249,22 +9249,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2037186036011676</v>
+        <v>0.2037998104275697</v>
       </c>
       <c r="C93">
-        <v>13.23200989238589</v>
+        <v>11.93027787112621</v>
       </c>
       <c r="D93">
-        <v>124.0000098923859</v>
+        <v>123.9362778711262</v>
       </c>
       <c r="E93">
-        <v>88.358</v>
+        <v>89.596</v>
       </c>
       <c r="F93">
-        <v>112.658</v>
+        <v>113.896</v>
       </c>
       <c r="G93">
         <v>1.89</v>
@@ -9285,28 +9285,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M93">
-        <v>10.13922</v>
+        <v>10.25064</v>
       </c>
       <c r="N93">
-        <v>5.484249387755101</v>
+        <v>5.372829387755102</v>
       </c>
       <c r="O93">
-        <v>0.8226374081632651</v>
+        <v>0.8059244081632653</v>
       </c>
       <c r="P93">
-        <v>4.661611979591836</v>
+        <v>4.566904979591837</v>
       </c>
       <c r="Q93">
-        <v>7.711611979591836</v>
+        <v>7.616904979591837</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.490040040012973</v>
+        <v>1.667747630344622</v>
       </c>
       <c r="T93">
-        <v>8.832792298900355</v>
+        <v>9.919629799488849</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.540894604097268</v>
+        <v>1.524145749704906</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9331,22 +9331,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2037998104275697</v>
+        <v>0.2038810172539718</v>
       </c>
       <c r="C94">
-        <v>11.93027787112621</v>
+        <v>10.62861132863529</v>
       </c>
       <c r="D94">
-        <v>123.9362778711262</v>
+        <v>123.8726113286353</v>
       </c>
       <c r="E94">
-        <v>89.596</v>
+        <v>90.834</v>
       </c>
       <c r="F94">
-        <v>113.896</v>
+        <v>115.134</v>
       </c>
       <c r="G94">
         <v>1.89</v>
@@ -9367,28 +9367,28 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M94">
-        <v>10.25064</v>
+        <v>10.36206</v>
       </c>
       <c r="N94">
-        <v>5.372829387755102</v>
+        <v>5.261409387755101</v>
       </c>
       <c r="O94">
-        <v>0.8059244081632653</v>
+        <v>0.7892114081632652</v>
       </c>
       <c r="P94">
-        <v>4.566904979591837</v>
+        <v>4.472197979591837</v>
       </c>
       <c r="Q94">
-        <v>7.616904979591837</v>
+        <v>7.522197979591836</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.667747630344622</v>
+        <v>1.896228817913885</v>
       </c>
       <c r="T94">
-        <v>9.919629799488849</v>
+        <v>11.31699230024548</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.524145749704906</v>
+        <v>1.507757085729585</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9413,22 +9413,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2038810172539718</v>
+        <v>0.2529281747182262</v>
       </c>
       <c r="C95">
-        <v>10.62861132863529</v>
+        <v>-19.94194799898442</v>
       </c>
       <c r="D95">
-        <v>123.8726113286353</v>
+        <v>94.54005200101558</v>
       </c>
       <c r="E95">
-        <v>90.834</v>
+        <v>92.072</v>
       </c>
       <c r="F95">
-        <v>115.134</v>
+        <v>116.372</v>
       </c>
       <c r="G95">
         <v>1.89</v>
@@ -9449,45 +9449,45 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M95">
-        <v>10.36206</v>
+        <v>17.0834096</v>
       </c>
       <c r="N95">
-        <v>5.261409387755101</v>
+        <v>-1.459940212244902</v>
       </c>
       <c r="O95">
-        <v>0.7892114081632652</v>
+        <v>-0.2189910318367353</v>
       </c>
       <c r="P95">
-        <v>4.472197979591837</v>
+        <v>-1.240949180408167</v>
       </c>
       <c r="Q95">
-        <v>7.522197979591836</v>
+        <v>1.809050819591833</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.896228817913885</v>
+        <v>2.231101082159353</v>
       </c>
       <c r="T95">
-        <v>11.31699230024548</v>
+        <v>13.36502938189026</v>
       </c>
       <c r="U95">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.15</v>
+        <v>0.1371810699992386</v>
       </c>
       <c r="W95">
-        <v>0.0765</v>
+        <v>0.1266618189241118</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>1.507757085729585</v>
+        <v>0.9145404666615907</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9495,22 +9495,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2529281747182262</v>
+        <v>0.2539381747182262</v>
       </c>
       <c r="C96">
-        <v>-19.94194799898442</v>
+        <v>-21.63870791964914</v>
       </c>
       <c r="D96">
-        <v>94.54005200101558</v>
+        <v>94.08129208035086</v>
       </c>
       <c r="E96">
-        <v>92.072</v>
+        <v>93.31</v>
       </c>
       <c r="F96">
-        <v>116.372</v>
+        <v>117.61</v>
       </c>
       <c r="G96">
         <v>1.89</v>
@@ -9531,37 +9531,37 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M96">
-        <v>17.0834096</v>
+        <v>17.265148</v>
       </c>
       <c r="N96">
-        <v>-1.459940212244902</v>
+        <v>-1.641678612244899</v>
       </c>
       <c r="O96">
-        <v>-0.2189910318367353</v>
+        <v>-0.2462517918367348</v>
       </c>
       <c r="P96">
-        <v>-1.240949180408167</v>
+        <v>-1.395426820408164</v>
       </c>
       <c r="Q96">
-        <v>1.809050819591833</v>
+        <v>1.654573179591836</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.231101082159353</v>
+        <v>2.668161298591226</v>
       </c>
       <c r="T96">
-        <v>13.36502938189026</v>
+        <v>16.03803525826832</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1371810699992386</v>
+        <v>0.1357370587360887</v>
       </c>
       <c r="W96">
-        <v>0.1266618189241118</v>
+        <v>0.1268737997775422</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.9145404666615907</v>
+        <v>0.9049137249072583</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9577,22 +9577,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2539381747182262</v>
+        <v>0.2549481747182262</v>
       </c>
       <c r="C97">
-        <v>-21.63870791964914</v>
+        <v>-23.33103703406371</v>
       </c>
       <c r="D97">
-        <v>94.08129208035086</v>
+        <v>93.6269629659363</v>
       </c>
       <c r="E97">
-        <v>93.31</v>
+        <v>94.54800000000002</v>
       </c>
       <c r="F97">
-        <v>117.61</v>
+        <v>118.848</v>
       </c>
       <c r="G97">
         <v>1.89</v>
@@ -9613,37 +9613,37 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M97">
-        <v>17.265148</v>
+        <v>17.4468864</v>
       </c>
       <c r="N97">
-        <v>-1.641678612244899</v>
+        <v>-1.823417012244903</v>
       </c>
       <c r="O97">
-        <v>-0.2462517918367348</v>
+        <v>-0.2735125518367355</v>
       </c>
       <c r="P97">
-        <v>-1.395426820408164</v>
+        <v>-1.549904460408168</v>
       </c>
       <c r="Q97">
-        <v>1.654573179591836</v>
+        <v>1.500095539591832</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.668161298591226</v>
+        <v>3.323751623239034</v>
       </c>
       <c r="T97">
-        <v>16.03803525826832</v>
+        <v>20.04754407283541</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1357370587360887</v>
+        <v>0.1343231310409211</v>
       </c>
       <c r="W97">
-        <v>0.1268737997775422</v>
+        <v>0.1270813643631928</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9049137249072583</v>
+        <v>0.8954875402728075</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9659,22 +9659,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2549481747182262</v>
+        <v>0.2559581747182262</v>
       </c>
       <c r="C98">
-        <v>-23.33103703406367</v>
+        <v>-25.01899922431576</v>
       </c>
       <c r="D98">
-        <v>93.62696296593633</v>
+        <v>93.17700077568423</v>
       </c>
       <c r="E98">
-        <v>94.548</v>
+        <v>95.786</v>
       </c>
       <c r="F98">
-        <v>118.848</v>
+        <v>120.086</v>
       </c>
       <c r="G98">
         <v>1.89</v>
@@ -9695,37 +9695,37 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M98">
-        <v>17.4468864</v>
+        <v>17.6286248</v>
       </c>
       <c r="N98">
-        <v>-1.823417012244899</v>
+        <v>-2.0051554122449</v>
       </c>
       <c r="O98">
-        <v>-0.2735125518367349</v>
+        <v>-0.3007733118367349</v>
       </c>
       <c r="P98">
-        <v>-1.549904460408164</v>
+        <v>-1.704382100408165</v>
       </c>
       <c r="Q98">
-        <v>1.500095539591835</v>
+        <v>1.345617899591835</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.323751623239025</v>
+        <v>4.4164021643187</v>
       </c>
       <c r="T98">
-        <v>20.04754407283535</v>
+        <v>26.73005876378047</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1343231310409211</v>
+        <v>0.1329383564941075</v>
       </c>
       <c r="W98">
-        <v>0.1270813643631928</v>
+        <v>0.127284649266665</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8954875402728076</v>
+        <v>0.8862557099607169</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9741,22 +9741,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2559581747182262</v>
+        <v>0.2569681747182261</v>
       </c>
       <c r="C99">
-        <v>-25.01899922431576</v>
+        <v>-26.70265715032197</v>
       </c>
       <c r="D99">
-        <v>93.17700077568423</v>
+        <v>92.73134284967803</v>
       </c>
       <c r="E99">
-        <v>95.786</v>
+        <v>97.024</v>
       </c>
       <c r="F99">
-        <v>120.086</v>
+        <v>121.324</v>
       </c>
       <c r="G99">
         <v>1.89</v>
@@ -9777,37 +9777,37 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M99">
-        <v>17.6286248</v>
+        <v>17.8103632</v>
       </c>
       <c r="N99">
-        <v>-2.0051554122449</v>
+        <v>-2.1868938122449</v>
       </c>
       <c r="O99">
-        <v>-0.3007733118367349</v>
+        <v>-0.328034071836735</v>
       </c>
       <c r="P99">
-        <v>-1.704382100408165</v>
+        <v>-1.858859740408165</v>
       </c>
       <c r="Q99">
-        <v>1.345617899591835</v>
+        <v>1.191140259591835</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.4164021643187</v>
+        <v>6.601703246478049</v>
       </c>
       <c r="T99">
-        <v>26.73005876378047</v>
+        <v>40.0950881456707</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1329383564941075</v>
+        <v>0.1315818426523309</v>
       </c>
       <c r="W99">
-        <v>0.127284649266665</v>
+        <v>0.1274837854986378</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8862557099607169</v>
+        <v>0.8772122843488728</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9823,22 +9823,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2569681747182261</v>
+        <v>0.2579781747182262</v>
       </c>
       <c r="C100">
-        <v>-26.70265715032197</v>
+        <v>-28.38207227891641</v>
       </c>
       <c r="D100">
-        <v>92.73134284967803</v>
+        <v>92.28992772108359</v>
       </c>
       <c r="E100">
-        <v>97.024</v>
+        <v>98.262</v>
       </c>
       <c r="F100">
-        <v>121.324</v>
+        <v>122.562</v>
       </c>
       <c r="G100">
         <v>1.89</v>
@@ -9859,37 +9859,37 @@
         <v>15.6234693877551</v>
       </c>
       <c r="M100">
-        <v>17.8103632</v>
+        <v>17.9921016</v>
       </c>
       <c r="N100">
-        <v>-2.1868938122449</v>
+        <v>-2.368632212244901</v>
       </c>
       <c r="O100">
-        <v>-0.328034071836735</v>
+        <v>-0.3552948318367351</v>
       </c>
       <c r="P100">
-        <v>-1.858859740408165</v>
+        <v>-2.013337380408165</v>
       </c>
       <c r="Q100">
-        <v>1.191140259591835</v>
+        <v>1.036662619591834</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.601703246478049</v>
+        <v>13.1576064929561</v>
       </c>
       <c r="T100">
-        <v>40.0950881456707</v>
+        <v>80.19017629134142</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1315818426523309</v>
+        <v>0.1302527331305902</v>
       </c>
       <c r="W100">
-        <v>0.1274837854986378</v>
+        <v>0.1276788987764294</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9897,91 +9897,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8772122843488728</v>
+        <v>0.8683515542039346</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2579781747182262</v>
-      </c>
-      <c r="C101">
-        <v>-28.38207227891641</v>
-      </c>
-      <c r="D101">
-        <v>92.28992772108359</v>
-      </c>
-      <c r="E101">
-        <v>98.262</v>
-      </c>
-      <c r="F101">
-        <v>122.562</v>
-      </c>
-      <c r="G101">
-        <v>1.89</v>
-      </c>
-      <c r="H101">
-        <v>99.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18.6734693877551</v>
-      </c>
-      <c r="K101">
-        <v>3.05</v>
-      </c>
-      <c r="L101">
-        <v>15.6234693877551</v>
-      </c>
-      <c r="M101">
-        <v>17.9921016</v>
-      </c>
-      <c r="N101">
-        <v>-2.368632212244901</v>
-      </c>
-      <c r="O101">
-        <v>-0.3552948318367351</v>
-      </c>
-      <c r="P101">
-        <v>-2.013337380408165</v>
-      </c>
-      <c r="Q101">
-        <v>1.036662619591834</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>13.1576064929561</v>
-      </c>
-      <c r="T101">
-        <v>80.19017629134142</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1302527331305902</v>
-      </c>
-      <c r="W101">
-        <v>0.1276788987764294</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8683515542039346</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
